--- a/data/k-props/2026-08-28.xlsx
+++ b/data/k-props/2026-08-28.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="93">
   <si>
     <t>date</t>
   </si>
@@ -133,157 +133,163 @@
     <t>08/28/2026</t>
   </si>
   <si>
+    <t>Jacob Lopez</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Athletics</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Brandon Young</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
     <t>Rhett Lowder</t>
   </si>
   <si>
     <t>Cincinnati Reds @ Chicago Cubs</t>
   </si>
   <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
+    <t>lineup_unweighted_30d_posted</t>
   </si>
   <si>
     <t>David Peterson</t>
   </si>
   <si>
-    <t>6-7</t>
+    <t>Tarik Skubal</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Detroit Tigers</t>
   </si>
   <si>
     <t>Drew Anderson</t>
   </si>
   <si>
-    <t>Los Angeles Dodgers @ Detroit Tigers</t>
-  </si>
-  <si>
     <t>Limited starter</t>
   </si>
   <si>
-    <t>Tarik Skubal</t>
-  </si>
-  <si>
-    <t>Eury Perez</t>
+    <t>Eury Pérez</t>
   </si>
   <si>
     <t>Miami Marlins @ Washington Nationals</t>
   </si>
   <si>
+    <t>Michael Wacha</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Tanner Bibee</t>
+  </si>
+  <si>
+    <t>Hunter Brown</t>
+  </si>
+  <si>
+    <t>Houston Astros @ New York Mets</t>
+  </si>
+  <si>
+    <t>Christian Scott</t>
+  </si>
+  <si>
+    <t>Casey Mize</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Shane McClanahan</t>
+  </si>
+  <si>
+    <t>Dylan Cease</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Tomoyuki Sugano</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Grant Holmes</t>
+  </si>
+  <si>
+    <t>Patrick Sandoval</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Cam Schlittler</t>
+  </si>
+  <si>
+    <t>Cody Bradford</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Logan Henderson</t>
+  </si>
+  <si>
+    <t>Luis Castillo</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Dean Kremer</t>
+  </si>
+  <si>
+    <t>Jared Jones</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ St. Louis Cardinals</t>
+  </si>
+  <si>
+    <t>Andrew Painter</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Reid Detmers</t>
+  </si>
+  <si>
+    <t>Kohl Drake</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>team_season_vs_hand</t>
+  </si>
+  <si>
+    <t>Blade Tidwell</t>
+  </si>
+  <si>
     <t>Jackson Kent</t>
   </si>
   <si>
-    <t>Tanner Bibee</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Michael Wacha</t>
-  </si>
-  <si>
-    <t>Christian Scott</t>
-  </si>
-  <si>
-    <t>Houston Astros @ New York Mets</t>
-  </si>
-  <si>
-    <t>Hunter Brown</t>
-  </si>
-  <si>
-    <t>Casey Mize</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Shane McClanahan</t>
-  </si>
-  <si>
-    <t>Grant Holmes</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Tomoyuki Sugano</t>
-  </si>
-  <si>
-    <t>Cam Schlittler</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Patrick Sandoval</t>
-  </si>
-  <si>
-    <t>Logan Henderson</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Cody Bradford</t>
-  </si>
-  <si>
-    <t>Luis Castillo</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Dean Kremer</t>
-  </si>
-  <si>
     <t>Quinn Mathews</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ St. Louis Cardinals</t>
-  </si>
-  <si>
-    <t>Jared Jones</t>
-  </si>
-  <si>
-    <t>Andrew Painter</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Reid Detmers</t>
-  </si>
-  <si>
-    <t>Dylan Cease</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Brandon Young</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ Athletics</t>
-  </si>
-  <si>
-    <t>Kohl Drake</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>team_season_vs_hand</t>
-  </si>
-  <si>
-    <t>Blade Tidwell</t>
   </si>
 </sst>
 </file>
@@ -664,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM29"/>
+  <dimension ref="A1:AM30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -797,73 +803,73 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D2">
-        <v>-140</v>
+        <v>117</v>
       </c>
       <c r="E2">
-        <v>116</v>
+        <v>-142</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>824638</v>
+        <v>824960</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
+        <v>4.7</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>5</v>
       </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
       <c r="M2">
-        <v>0.1736</v>
+        <v>0.2148</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="P2">
-        <v>4.47</v>
+        <v>4.46</v>
       </c>
       <c r="Q2">
-        <v>0.144</v>
+        <v>0.3162</v>
       </c>
       <c r="R2">
-        <v>0.385</v>
+        <v>0.369</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2104</v>
+        <v>0.2627</v>
       </c>
       <c r="U2">
-        <v>0.2077</v>
+        <v>0.2436</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2164</v>
+        <v>0.2586</v>
       </c>
       <c r="X2">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y2">
-        <v>0.9871</v>
+        <v>1.0521</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -872,22 +878,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>3.54</v>
+        <v>6.79</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.1622</v>
+        <v>0.247</v>
       </c>
       <c r="AG2">
-        <v>0.989</v>
+        <v>1.2363</v>
       </c>
       <c r="AH2">
-        <v>0.22</v>
+        <v>-0.58</v>
       </c>
       <c r="AM2">
-        <v>3.76</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -901,22 +907,22 @@
         <v>4.5</v>
       </c>
       <c r="D3">
-        <v>-156</v>
+        <v>123</v>
       </c>
       <c r="E3">
-        <v>122</v>
+        <v>-142</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
       <c r="G3">
-        <v>824638</v>
+        <v>824960</v>
       </c>
       <c r="H3" t="s">
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -925,46 +931,46 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>0.1936</v>
+        <v>0.1871</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="P3">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="Q3">
-        <v>0.2295</v>
+        <v>0.1667</v>
       </c>
       <c r="R3">
-        <v>0.379</v>
+        <v>0.363</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.266</v>
+        <v>0.2591</v>
       </c>
       <c r="U3">
-        <v>0.2708</v>
+        <v>0.2289</v>
       </c>
       <c r="V3">
         <v>8</v>
       </c>
       <c r="W3">
-        <v>0.2487</v>
+        <v>0.2148</v>
       </c>
       <c r="X3">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y3">
-        <v>1.039</v>
+        <v>1.0344</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -973,22 +979,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>6.15</v>
+        <v>5.45</v>
       </c>
       <c r="AE3" t="s">
         <v>47</v>
       </c>
       <c r="AF3">
-        <v>0.2072</v>
+        <v>0.1797</v>
       </c>
       <c r="AG3">
-        <v>1.2503</v>
+        <v>1.2197</v>
       </c>
       <c r="AH3">
-        <v>-0.57</v>
+        <v>0.24</v>
       </c>
       <c r="AM3">
-        <v>5.58</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -999,25 +1005,25 @@
         <v>48</v>
       </c>
       <c r="C4">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D4">
-        <v>-103</v>
+        <v>-140</v>
       </c>
       <c r="E4">
-        <v>-120</v>
+        <v>116</v>
       </c>
       <c r="F4" t="s">
         <v>49</v>
       </c>
       <c r="G4">
-        <v>824231</v>
+        <v>824638</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I4">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1029,43 +1035,43 @@
         <v>4</v>
       </c>
       <c r="M4">
-        <v>0.2615</v>
+        <v>0.1736</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="P4">
-        <v>4.28</v>
+        <v>4.47</v>
       </c>
       <c r="Q4">
-        <v>0.2143</v>
+        <v>0.144</v>
       </c>
       <c r="R4">
-        <v>0.296</v>
+        <v>0.385</v>
       </c>
       <c r="S4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="T4">
-        <v>0.2251</v>
+        <v>0.2076</v>
       </c>
       <c r="U4">
-        <v>0.1979</v>
+        <v>0.2062</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2067</v>
+        <v>0.2164</v>
       </c>
       <c r="X4">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y4">
-        <v>1.0011</v>
+        <v>0.9439</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1074,22 +1080,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>4.67</v>
+        <v>3.34</v>
       </c>
       <c r="AE4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF4">
-        <v>0.2475</v>
+        <v>0.1622</v>
       </c>
       <c r="AG4">
-        <v>1.0579</v>
+        <v>0.977</v>
       </c>
       <c r="AH4">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AM4">
-        <v>4.89</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1100,25 +1106,25 @@
         <v>51</v>
       </c>
       <c r="C5">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D5">
         <v>-156</v>
       </c>
       <c r="E5">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F5" t="s">
         <v>49</v>
       </c>
       <c r="G5">
-        <v>824231</v>
+        <v>824638</v>
       </c>
       <c r="H5" t="s">
         <v>42</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1130,43 +1136,43 @@
         <v>4</v>
       </c>
       <c r="M5">
-        <v>0.3087</v>
+        <v>0.1936</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="P5">
-        <v>3.92</v>
+        <v>4.5</v>
       </c>
       <c r="Q5">
-        <v>0.2903</v>
+        <v>0.2295</v>
       </c>
       <c r="R5">
-        <v>0.383</v>
+        <v>0.379</v>
       </c>
       <c r="S5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="T5">
-        <v>0.1777</v>
+        <v>0.2592</v>
       </c>
       <c r="U5">
-        <v>0.1958</v>
+        <v>0.2661</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2272</v>
+        <v>0.2487</v>
       </c>
       <c r="X5">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y5">
-        <v>0.9797</v>
+        <v>1.0713</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1175,22 +1181,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>5.84</v>
+        <v>6.18</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.3016</v>
+        <v>0.2072</v>
       </c>
       <c r="AG5">
-        <v>0.8353</v>
+        <v>1.22</v>
       </c>
       <c r="AH5">
-        <v>0.22</v>
+        <v>-0.58</v>
       </c>
       <c r="AM5">
-        <v>6.06</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1201,25 +1207,25 @@
         <v>52</v>
       </c>
       <c r="C6">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D6">
-        <v>-111</v>
+        <v>-156</v>
       </c>
       <c r="E6">
-        <v>-111</v>
+        <v>130</v>
       </c>
       <c r="F6" t="s">
         <v>53</v>
       </c>
       <c r="G6">
-        <v>822691</v>
+        <v>824231</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
       </c>
       <c r="I6">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1231,43 +1237,43 @@
         <v>4</v>
       </c>
       <c r="M6">
-        <v>0.266</v>
+        <v>0.3087</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="P6">
-        <v>4.03</v>
+        <v>3.92</v>
       </c>
       <c r="Q6">
-        <v>0.2672</v>
+        <v>0.2903</v>
       </c>
       <c r="R6">
-        <v>0.367</v>
+        <v>0.383</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>0.2282</v>
+        <v>0.1777</v>
       </c>
       <c r="U6">
-        <v>0.2321</v>
+        <v>0.1958</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>0.2058</v>
+        <v>0.2272</v>
       </c>
       <c r="X6">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y6">
-        <v>1.0147</v>
+        <v>0.9799</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1276,22 +1282,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>6.49</v>
+        <v>5.85</v>
       </c>
       <c r="AE6" t="s">
         <v>47</v>
       </c>
       <c r="AF6">
-        <v>0.2665</v>
+        <v>0.3016</v>
       </c>
       <c r="AG6">
-        <v>1.0723</v>
+        <v>0.8366</v>
       </c>
       <c r="AH6">
-        <v>-0.57</v>
+        <v>0.24</v>
       </c>
       <c r="AM6">
-        <v>5.92</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1302,31 +1308,73 @@
         <v>54</v>
       </c>
       <c r="C7">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D7">
-        <v>-170</v>
+        <v>-103</v>
       </c>
       <c r="E7">
-        <v>132</v>
+        <v>-120</v>
       </c>
       <c r="F7" t="s">
         <v>53</v>
       </c>
-      <c r="G7" t="s">
-        <v>44</v>
+      <c r="G7">
+        <v>824231</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="I7">
+        <v>4.2</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
       </c>
       <c r="L7">
         <v>4</v>
       </c>
+      <c r="M7">
+        <v>0.2615</v>
+      </c>
+      <c r="N7">
+        <v>5</v>
+      </c>
+      <c r="O7">
+        <v>84</v>
+      </c>
+      <c r="P7">
+        <v>4.28</v>
+      </c>
+      <c r="Q7">
+        <v>0.2143</v>
+      </c>
+      <c r="R7">
+        <v>0.296</v>
+      </c>
       <c r="S7" t="s">
-        <v>44</v>
-      </c>
-      <c r="V7" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T7">
+        <v>0.2251</v>
+      </c>
+      <c r="U7">
+        <v>0.1979</v>
+      </c>
+      <c r="V7">
+        <v>8</v>
+      </c>
+      <c r="W7">
+        <v>0.2067</v>
+      </c>
+      <c r="X7">
+        <v>0.2124</v>
+      </c>
+      <c r="Y7">
+        <v>1.0009</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1334,8 +1382,23 @@
       <c r="AC7" t="s">
         <v>44</v>
       </c>
+      <c r="AD7">
+        <v>4.68</v>
+      </c>
       <c r="AE7" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="AF7">
+        <v>0.2475</v>
+      </c>
+      <c r="AG7">
+        <v>1.0596</v>
+      </c>
+      <c r="AH7">
+        <v>0.24</v>
+      </c>
+      <c r="AM7">
+        <v>4.92</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1343,28 +1406,28 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D8">
-        <v>-132</v>
+        <v>-111</v>
       </c>
       <c r="E8">
-        <v>106</v>
+        <v>-111</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8">
-        <v>824396</v>
+        <v>822691</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1373,46 +1436,46 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8">
-        <v>0.1931</v>
+        <v>0.266</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="P8">
-        <v>4.07</v>
+        <v>4.03</v>
       </c>
       <c r="Q8">
-        <v>0.2047</v>
+        <v>0.2672</v>
       </c>
       <c r="R8">
-        <v>0.388</v>
+        <v>0.367</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.173</v>
+        <v>0.2282</v>
       </c>
       <c r="U8">
-        <v>0.1875</v>
+        <v>0.2321</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2075</v>
+        <v>0.2058</v>
       </c>
       <c r="X8">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y8">
-        <v>0.9622</v>
+        <v>1.0153</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1421,22 +1484,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>3.65</v>
+        <v>6.51</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.1976</v>
+        <v>0.2665</v>
       </c>
       <c r="AG8">
-        <v>0.8132</v>
+        <v>1.074</v>
       </c>
       <c r="AH8">
-        <v>0.22</v>
+        <v>-0.58</v>
       </c>
       <c r="AM8">
-        <v>3.87</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1444,7 +1507,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9">
         <v>4.5</v>
@@ -1456,7 +1519,7 @@
         <v>-160</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>824396</v>
@@ -1510,10 +1573,10 @@
         <v>0.2103</v>
       </c>
       <c r="X9">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y9">
-        <v>0.9476</v>
+        <v>0.9478</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1522,22 +1585,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.23</v>
+        <v>4.24</v>
       </c>
       <c r="AE9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF9">
         <v>0.1884</v>
       </c>
       <c r="AG9">
-        <v>0.9356</v>
+        <v>0.9371</v>
       </c>
       <c r="AH9">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AM9">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1545,28 +1608,28 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C10">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D10">
-        <v>-149</v>
+        <v>-132</v>
       </c>
       <c r="E10">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="F10" t="s">
         <v>59</v>
       </c>
       <c r="G10">
-        <v>823583</v>
+        <v>824396</v>
       </c>
       <c r="H10" t="s">
         <v>42</v>
       </c>
       <c r="I10">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1578,43 +1641,43 @@
         <v>3</v>
       </c>
       <c r="M10">
-        <v>0.2846</v>
+        <v>0.1931</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="P10">
-        <v>4.37</v>
+        <v>4.07</v>
       </c>
       <c r="Q10">
-        <v>0.2773</v>
+        <v>0.2047</v>
       </c>
       <c r="R10">
-        <v>0.373</v>
+        <v>0.388</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2264</v>
+        <v>0.173</v>
       </c>
       <c r="U10">
-        <v>0.2164</v>
+        <v>0.1875</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2191</v>
+        <v>0.2075</v>
       </c>
       <c r="X10">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y10">
-        <v>1.0137</v>
+        <v>0.9621</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1623,22 +1686,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>6.24</v>
+        <v>3.65</v>
       </c>
       <c r="AE10" t="s">
         <v>47</v>
       </c>
       <c r="AF10">
-        <v>0.2819</v>
+        <v>0.1976</v>
       </c>
       <c r="AG10">
-        <v>1.064</v>
+        <v>0.8145</v>
       </c>
       <c r="AH10">
-        <v>-0.57</v>
+        <v>0.24</v>
       </c>
       <c r="AM10">
-        <v>5.67</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1646,7 +1709,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>5.5</v>
@@ -1658,7 +1721,7 @@
         <v>-135</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G11">
         <v>823583</v>
@@ -1712,10 +1775,10 @@
         <v>0.2232</v>
       </c>
       <c r="X11">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y11">
-        <v>0.9899</v>
+        <v>0.9924</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1724,22 +1787,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.8</v>
+        <v>5.83</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF11">
         <v>0.2357</v>
       </c>
       <c r="AG11">
-        <v>1.1051</v>
+        <v>1.1069</v>
       </c>
       <c r="AH11">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AM11">
-        <v>6.02</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1747,28 +1810,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C12">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D12">
-        <v>-136</v>
+        <v>-149</v>
       </c>
       <c r="E12">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="F12" t="s">
         <v>62</v>
       </c>
       <c r="G12">
-        <v>822935</v>
+        <v>823583</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
       </c>
       <c r="I12">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1780,43 +1843,43 @@
         <v>3</v>
       </c>
       <c r="M12">
-        <v>0.2257</v>
+        <v>0.2846</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="P12">
-        <v>4.02</v>
+        <v>4.37</v>
       </c>
       <c r="Q12">
-        <v>0.1287</v>
+        <v>0.2773</v>
       </c>
       <c r="R12">
-        <v>0.336</v>
+        <v>0.373</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
       </c>
       <c r="T12">
-        <v>0.1603</v>
+        <v>0.2264</v>
       </c>
       <c r="U12">
-        <v>0.1542</v>
+        <v>0.2164</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>0.187</v>
+        <v>0.2191</v>
       </c>
       <c r="X12">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y12">
-        <v>0.9142</v>
+        <v>1.0154</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1825,22 +1888,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>2.8</v>
+        <v>6.26</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.1931</v>
+        <v>0.2819</v>
       </c>
       <c r="AG12">
-        <v>0.7532</v>
+        <v>1.0657</v>
       </c>
       <c r="AH12">
-        <v>0.22</v>
+        <v>-0.58</v>
       </c>
       <c r="AM12">
-        <v>3.02</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1848,19 +1911,19 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D13">
-        <v>-104</v>
+        <v>-136</v>
       </c>
       <c r="E13">
-        <v>-122</v>
+        <v>110</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G13">
         <v>822935</v>
@@ -1869,7 +1932,7 @@
         <v>42</v>
       </c>
       <c r="I13">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1881,43 +1944,43 @@
         <v>3</v>
       </c>
       <c r="M13">
-        <v>0.2235</v>
+        <v>0.2257</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="P13">
-        <v>4.13</v>
+        <v>4.02</v>
       </c>
       <c r="Q13">
-        <v>0.191</v>
+        <v>0.1287</v>
       </c>
       <c r="R13">
-        <v>0.308</v>
+        <v>0.336</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
       </c>
       <c r="T13">
-        <v>0.1879</v>
+        <v>0.1603</v>
       </c>
       <c r="U13">
-        <v>0.1901</v>
+        <v>0.1542</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2232</v>
+        <v>0.187</v>
       </c>
       <c r="X13">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y13">
-        <v>0.9895</v>
+        <v>0.9142</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1926,22 +1989,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>3.76</v>
+        <v>2.8</v>
       </c>
       <c r="AE13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF13">
-        <v>0.2135</v>
+        <v>0.1931</v>
       </c>
       <c r="AG13">
-        <v>0.883</v>
+        <v>0.7544</v>
       </c>
       <c r="AH13">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AM13">
-        <v>3.98</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1949,28 +2012,28 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14">
         <v>4.5</v>
       </c>
       <c r="D14">
-        <v>-111</v>
+        <v>-104</v>
       </c>
       <c r="E14">
-        <v>-115</v>
+        <v>-122</v>
       </c>
       <c r="F14" t="s">
         <v>65</v>
       </c>
       <c r="G14">
-        <v>824877</v>
+        <v>822935</v>
       </c>
       <c r="H14" t="s">
         <v>42</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1979,46 +2042,46 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M14">
-        <v>0.189</v>
+        <v>0.2235</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="P14">
-        <v>4.28</v>
+        <v>4.13</v>
       </c>
       <c r="Q14">
-        <v>0.1589</v>
+        <v>0.191</v>
       </c>
       <c r="R14">
-        <v>0.349</v>
+        <v>0.308</v>
       </c>
       <c r="S14" t="s">
         <v>43</v>
       </c>
       <c r="T14">
-        <v>0.2137</v>
+        <v>0.1879</v>
       </c>
       <c r="U14">
-        <v>0.2098</v>
+        <v>0.1901</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>0.2184</v>
+        <v>0.2232</v>
       </c>
       <c r="X14">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y14">
-        <v>1.0257</v>
+        <v>0.9895</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2027,22 +2090,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>3.92</v>
+        <v>3.76</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF14">
-        <v>0.1785</v>
+        <v>0.2135</v>
       </c>
       <c r="AG14">
-        <v>1.0046</v>
+        <v>0.8844</v>
       </c>
       <c r="AH14">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AM14">
-        <v>4.14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2050,28 +2113,19 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15">
-        <v>2.5</v>
-      </c>
-      <c r="D15">
-        <v>-186</v>
-      </c>
-      <c r="E15">
-        <v>145</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G15">
-        <v>824877</v>
+        <v>822769</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2080,46 +2134,46 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>0.1376</v>
+        <v>0.361</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="P15">
-        <v>4.24</v>
+        <v>4.01</v>
       </c>
       <c r="Q15">
-        <v>0.1351</v>
+        <v>0.3443</v>
       </c>
       <c r="R15">
-        <v>0.357</v>
+        <v>0.379</v>
       </c>
       <c r="S15" t="s">
         <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2292</v>
+        <v>0.2187</v>
       </c>
       <c r="U15">
-        <v>0.226</v>
+        <v>0.2249</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2212</v>
+        <v>0.2256</v>
       </c>
       <c r="X15">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y15">
-        <v>0.9933</v>
+        <v>0.9889</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2128,22 +2182,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>3.28</v>
+        <v>8.71</v>
       </c>
       <c r="AE15" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="AF15">
-        <v>0.1367</v>
+        <v>0.3546</v>
       </c>
       <c r="AG15">
-        <v>1.0772</v>
+        <v>1.0294</v>
       </c>
       <c r="AH15">
-        <v>0.22</v>
+        <v>-0.95</v>
       </c>
       <c r="AM15">
-        <v>3.5</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2151,28 +2205,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C16">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="D16">
-        <v>-130</v>
+        <v>-186</v>
       </c>
       <c r="E16">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G16">
-        <v>823504</v>
+        <v>824877</v>
       </c>
       <c r="H16" t="s">
         <v>42</v>
       </c>
       <c r="I16">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2181,46 +2235,46 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M16">
-        <v>0.3078</v>
+        <v>0.1376</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P16">
-        <v>3.97</v>
+        <v>4.24</v>
       </c>
       <c r="Q16">
-        <v>0.3214</v>
+        <v>0.1351</v>
       </c>
       <c r="R16">
-        <v>0.359</v>
+        <v>0.357</v>
       </c>
       <c r="S16" t="s">
         <v>43</v>
       </c>
       <c r="T16">
-        <v>0.188</v>
+        <v>0.2292</v>
       </c>
       <c r="U16">
-        <v>0.1848</v>
+        <v>0.226</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2131</v>
+        <v>0.2212</v>
       </c>
       <c r="X16">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y16">
-        <v>0.9878</v>
+        <v>0.9945</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2229,22 +2283,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>6.34</v>
+        <v>3.29</v>
       </c>
       <c r="AE16" t="s">
         <v>47</v>
       </c>
       <c r="AF16">
-        <v>0.3127</v>
+        <v>0.1367</v>
       </c>
       <c r="AG16">
-        <v>0.8836</v>
+        <v>1.0789</v>
       </c>
       <c r="AH16">
-        <v>-0.57</v>
+        <v>0.24</v>
       </c>
       <c r="AM16">
-        <v>5.77</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2252,22 +2306,22 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C17">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D17">
-        <v>-119</v>
+        <v>-111</v>
       </c>
       <c r="E17">
-        <v>-104</v>
+        <v>-115</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G17">
-        <v>823504</v>
+        <v>824877</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
@@ -2282,46 +2336,46 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M17">
-        <v>0.2228</v>
+        <v>0.189</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="P17">
-        <v>4.64</v>
+        <v>4.28</v>
       </c>
       <c r="Q17">
-        <v>0.2333</v>
+        <v>0.1589</v>
       </c>
       <c r="R17">
-        <v>0.375</v>
+        <v>0.349</v>
       </c>
       <c r="S17" t="s">
         <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2361</v>
+        <v>0.2137</v>
       </c>
       <c r="U17">
-        <v>0.2453</v>
+        <v>0.2098</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2479</v>
+        <v>0.2184</v>
       </c>
       <c r="X17">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y17">
-        <v>0.9829</v>
+        <v>1.0239</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2330,22 +2384,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>5.69</v>
+        <v>3.92</v>
       </c>
       <c r="AE17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF17">
-        <v>0.2268</v>
+        <v>0.1785</v>
       </c>
       <c r="AG17">
-        <v>1.1097</v>
+        <v>1.0061</v>
       </c>
       <c r="AH17">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AM17">
-        <v>5.91</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2353,28 +2407,28 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C18">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D18">
-        <v>-113</v>
+        <v>-119</v>
       </c>
       <c r="E18">
-        <v>-111</v>
+        <v>-104</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G18">
-        <v>823744</v>
+        <v>823504</v>
       </c>
       <c r="H18" t="s">
         <v>42</v>
       </c>
       <c r="I18">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2383,46 +2437,46 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M18">
-        <v>0.2992</v>
+        <v>0.2228</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P18">
-        <v>3.81</v>
+        <v>4.64</v>
       </c>
       <c r="Q18">
-        <v>0.2759</v>
+        <v>0.2333</v>
       </c>
       <c r="R18">
-        <v>0.367</v>
+        <v>0.375</v>
       </c>
       <c r="S18" t="s">
         <v>43</v>
       </c>
       <c r="T18">
-        <v>0.2247</v>
+        <v>0.2361</v>
       </c>
       <c r="U18">
-        <v>0.236</v>
+        <v>0.2453</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>0.223</v>
+        <v>0.2479</v>
       </c>
       <c r="X18">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y18">
-        <v>1.0377</v>
+        <v>0.984</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2431,22 +2485,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>6.47</v>
+        <v>5.7</v>
       </c>
       <c r="AE18" t="s">
         <v>47</v>
       </c>
       <c r="AF18">
-        <v>0.2907</v>
+        <v>0.2268</v>
       </c>
       <c r="AG18">
-        <v>1.0561</v>
+        <v>1.1114</v>
       </c>
       <c r="AH18">
-        <v>-0.57</v>
+        <v>0.24</v>
       </c>
       <c r="AM18">
-        <v>5.9</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2454,28 +2508,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C19">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D19">
-        <v>-140</v>
+        <v>-130</v>
       </c>
       <c r="E19">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="F19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G19">
-        <v>823744</v>
+        <v>823504</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2484,46 +2538,46 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M19">
-        <v>0.1494</v>
+        <v>0.3078</v>
       </c>
       <c r="N19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="P19">
-        <v>4.21</v>
+        <v>3.97</v>
       </c>
       <c r="Q19">
-        <v>0.1494</v>
+        <v>0.3214</v>
       </c>
       <c r="R19">
-        <v>0.303</v>
+        <v>0.359</v>
       </c>
       <c r="S19" t="s">
         <v>43</v>
       </c>
       <c r="T19">
-        <v>0.216</v>
+        <v>0.188</v>
       </c>
       <c r="U19">
-        <v>0.2169</v>
+        <v>0.1848</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>0.2175</v>
+        <v>0.2131</v>
       </c>
       <c r="X19">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y19">
-        <v>1.0136</v>
+        <v>0.9872</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2532,22 +2586,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>3.34</v>
+        <v>6.34</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.1494</v>
+        <v>0.3127</v>
       </c>
       <c r="AG19">
-        <v>1.0152</v>
+        <v>0.885</v>
       </c>
       <c r="AH19">
-        <v>0.22</v>
+        <v>-0.58</v>
       </c>
       <c r="AM19">
-        <v>3.56</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2555,28 +2609,28 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C20">
         <v>3.5</v>
       </c>
       <c r="D20">
-        <v>-170</v>
+        <v>-140</v>
       </c>
       <c r="E20">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="F20" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G20">
-        <v>823666</v>
+        <v>823744</v>
       </c>
       <c r="H20" t="s">
         <v>42</v>
       </c>
       <c r="I20">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2585,46 +2639,46 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M20">
-        <v>0.2</v>
+        <v>0.1494</v>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O20">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="P20">
-        <v>4.45</v>
+        <v>4.21</v>
       </c>
       <c r="Q20">
-        <v>0.1944</v>
+        <v>0.1494</v>
       </c>
       <c r="R20">
-        <v>0.351</v>
+        <v>0.303</v>
       </c>
       <c r="S20" t="s">
         <v>43</v>
       </c>
       <c r="T20">
-        <v>0.1887</v>
+        <v>0.216</v>
       </c>
       <c r="U20">
-        <v>0.1857</v>
+        <v>0.2169</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2077</v>
+        <v>0.2175</v>
       </c>
       <c r="X20">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y20">
-        <v>0.9753</v>
+        <v>1.0116</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2633,22 +2687,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>3.87</v>
+        <v>3.34</v>
       </c>
       <c r="AE20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF20">
-        <v>0.1981</v>
+        <v>0.1494</v>
       </c>
       <c r="AG20">
-        <v>0.887</v>
+        <v>1.0168</v>
       </c>
       <c r="AH20">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AM20">
-        <v>4.09</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2656,22 +2710,22 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C21">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D21">
-        <v>110</v>
+        <v>-113</v>
       </c>
       <c r="E21">
-        <v>-138</v>
+        <v>-111</v>
       </c>
       <c r="F21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G21">
-        <v>823666</v>
+        <v>823744</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
@@ -2686,46 +2740,46 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21">
-        <v>0.2427</v>
+        <v>0.2992</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="P21">
-        <v>4.07</v>
+        <v>3.81</v>
       </c>
       <c r="Q21">
-        <v>0.2202</v>
+        <v>0.2759</v>
       </c>
       <c r="R21">
-        <v>0.353</v>
+        <v>0.367</v>
       </c>
       <c r="S21" t="s">
         <v>43</v>
       </c>
       <c r="T21">
-        <v>0.2261</v>
+        <v>0.2247</v>
       </c>
       <c r="U21">
-        <v>0.248</v>
+        <v>0.236</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>0.2369</v>
+        <v>0.223</v>
       </c>
       <c r="X21">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y21">
-        <v>1.0342</v>
+        <v>1.0375</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2734,22 +2788,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.61</v>
+        <v>6.48</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
       </c>
       <c r="AF21">
-        <v>0.2347</v>
+        <v>0.2907</v>
       </c>
       <c r="AG21">
-        <v>1.0627</v>
+        <v>1.0578</v>
       </c>
       <c r="AH21">
-        <v>0.22</v>
+        <v>-0.58</v>
       </c>
       <c r="AM21">
-        <v>5.83</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2757,34 +2811,76 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C22">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D22">
-        <v>-162</v>
+        <v>-170</v>
       </c>
       <c r="E22">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="F22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G22" t="s">
-        <v>44</v>
+        <v>80</v>
+      </c>
+      <c r="G22">
+        <v>823666</v>
       </c>
       <c r="H22" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I22">
+        <v>5.1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="M22">
+        <v>0.2</v>
+      </c>
+      <c r="N22">
+        <v>5</v>
+      </c>
+      <c r="O22">
+        <v>108</v>
+      </c>
+      <c r="P22">
+        <v>4.45</v>
+      </c>
+      <c r="Q22">
+        <v>0.1944</v>
+      </c>
+      <c r="R22">
+        <v>0.351</v>
       </c>
       <c r="S22" t="s">
-        <v>44</v>
-      </c>
-      <c r="V22" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T22">
+        <v>0.1887</v>
+      </c>
+      <c r="U22">
+        <v>0.1857</v>
+      </c>
+      <c r="V22">
+        <v>9</v>
+      </c>
+      <c r="W22">
+        <v>0.2077</v>
+      </c>
+      <c r="X22">
+        <v>0.2124</v>
+      </c>
+      <c r="Y22">
+        <v>0.9752</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2792,8 +2888,23 @@
       <c r="AC22" t="s">
         <v>44</v>
       </c>
+      <c r="AD22">
+        <v>3.88</v>
+      </c>
       <c r="AE22" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="AF22">
+        <v>0.1981</v>
+      </c>
+      <c r="AG22">
+        <v>0.8884</v>
+      </c>
+      <c r="AH22">
+        <v>0.24</v>
+      </c>
+      <c r="AM22">
+        <v>4.12</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2801,28 +2912,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C23">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D23">
-        <v>-130</v>
+        <v>110</v>
       </c>
       <c r="E23">
-        <v>115</v>
+        <v>-138</v>
       </c>
       <c r="F23" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G23">
-        <v>823013</v>
+        <v>823666</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2831,46 +2942,46 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M23">
-        <v>0.2664</v>
+        <v>0.2427</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="P23">
-        <v>4.25</v>
+        <v>4.07</v>
       </c>
       <c r="Q23">
-        <v>0.2286</v>
+        <v>0.2202</v>
       </c>
       <c r="R23">
-        <v>0.344</v>
+        <v>0.353</v>
       </c>
       <c r="S23" t="s">
         <v>43</v>
       </c>
       <c r="T23">
-        <v>0.2404</v>
+        <v>0.2261</v>
       </c>
       <c r="U23">
-        <v>0.2045</v>
+        <v>0.248</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2155</v>
+        <v>0.2369</v>
       </c>
       <c r="X23">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y23">
-        <v>0.9556</v>
+        <v>1.0341</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2879,22 +2990,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>5.27</v>
+        <v>5.61</v>
       </c>
       <c r="AE23" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF23">
-        <v>0.2534</v>
+        <v>0.2347</v>
       </c>
       <c r="AG23">
-        <v>1.13</v>
+        <v>1.0644</v>
       </c>
       <c r="AH23">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AM23">
-        <v>5.49</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2902,28 +3013,28 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C24">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D24">
-        <v>122</v>
+        <v>-130</v>
       </c>
       <c r="E24">
-        <v>-156</v>
+        <v>115</v>
       </c>
       <c r="F24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G24">
-        <v>823985</v>
+        <v>823013</v>
       </c>
       <c r="H24" t="s">
         <v>42</v>
       </c>
       <c r="I24">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -2932,46 +3043,46 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M24">
-        <v>0.1927</v>
+        <v>0.2664</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="P24">
-        <v>4.44</v>
+        <v>4.25</v>
       </c>
       <c r="Q24">
-        <v>0.2342</v>
+        <v>0.2286</v>
       </c>
       <c r="R24">
-        <v>0.357</v>
+        <v>0.344</v>
       </c>
       <c r="S24" t="s">
         <v>43</v>
       </c>
       <c r="T24">
-        <v>0.2562</v>
+        <v>0.2404</v>
       </c>
       <c r="U24">
-        <v>0.2478</v>
+        <v>0.2045</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>0.252</v>
+        <v>0.2155</v>
       </c>
       <c r="X24">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y24">
-        <v>1.0402</v>
+        <v>0.9549</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -2980,22 +3091,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>5.59</v>
+        <v>5.28</v>
       </c>
       <c r="AE24" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF24">
-        <v>0.2075</v>
+        <v>0.2534</v>
       </c>
       <c r="AG24">
-        <v>1.2042</v>
+        <v>1.1318</v>
       </c>
       <c r="AH24">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AM24">
-        <v>5.81</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3003,19 +3114,19 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C25">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D25">
-        <v>-125</v>
+        <v>122</v>
       </c>
       <c r="E25">
-        <v>-102</v>
+        <v>-156</v>
       </c>
       <c r="F25" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G25">
         <v>823985</v>
@@ -3024,7 +3135,7 @@
         <v>42</v>
       </c>
       <c r="I25">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -3036,43 +3147,43 @@
         <v>2</v>
       </c>
       <c r="M25">
-        <v>0.2852</v>
+        <v>0.1927</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P25">
-        <v>4.05</v>
+        <v>4.44</v>
       </c>
       <c r="Q25">
-        <v>0.3273</v>
+        <v>0.2342</v>
       </c>
       <c r="R25">
-        <v>0.355</v>
+        <v>0.357</v>
       </c>
       <c r="S25" t="s">
         <v>43</v>
       </c>
       <c r="T25">
-        <v>0.1526</v>
+        <v>0.2562</v>
       </c>
       <c r="U25">
-        <v>0.1542</v>
+        <v>0.2478</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2269</v>
+        <v>0.252</v>
       </c>
       <c r="X25">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y25">
-        <v>0.9582</v>
+        <v>1.0402</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3081,22 +3192,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>4.78</v>
+        <v>5.6</v>
       </c>
       <c r="AE25" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF25">
-        <v>0.3002</v>
+        <v>0.2075</v>
       </c>
       <c r="AG25">
-        <v>0.7172</v>
+        <v>1.2061</v>
       </c>
       <c r="AH25">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AM25">
-        <v>5</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3104,19 +3215,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>86</v>
+      </c>
+      <c r="C26">
+        <v>6.5</v>
+      </c>
+      <c r="D26">
+        <v>-125</v>
+      </c>
+      <c r="E26">
+        <v>-102</v>
       </c>
       <c r="F26" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G26">
-        <v>822769</v>
+        <v>823985</v>
       </c>
       <c r="H26" t="s">
         <v>42</v>
       </c>
       <c r="I26">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3125,46 +3245,46 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26">
-        <v>0.361</v>
+        <v>0.2852</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="P26">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="Q26">
-        <v>0.3443</v>
+        <v>0.3273</v>
       </c>
       <c r="R26">
-        <v>0.379</v>
+        <v>0.355</v>
       </c>
       <c r="S26" t="s">
         <v>43</v>
       </c>
       <c r="T26">
-        <v>0.2187</v>
+        <v>0.1526</v>
       </c>
       <c r="U26">
-        <v>0.2249</v>
+        <v>0.1542</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2256</v>
+        <v>0.2269</v>
       </c>
       <c r="X26">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y26">
-        <v>0.9887</v>
+        <v>0.9584</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3173,22 +3293,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>8.69</v>
+        <v>4.79</v>
       </c>
       <c r="AE26" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="AF26">
-        <v>0.3546</v>
+        <v>0.3002</v>
       </c>
       <c r="AG26">
-        <v>1.0277</v>
+        <v>0.7183</v>
       </c>
       <c r="AH26">
-        <v>-1.07</v>
+        <v>0.24</v>
       </c>
       <c r="AM26">
-        <v>7.62</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3196,19 +3316,19 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G27">
-        <v>824960</v>
+        <v>823178</v>
       </c>
       <c r="H27" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="I27">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3220,43 +3340,37 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0.1871</v>
+        <v>0.1688</v>
       </c>
       <c r="N27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O27">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="P27">
-        <v>4.29</v>
+        <v>4.62</v>
       </c>
       <c r="Q27">
-        <v>0.1667</v>
+        <v>0.1688</v>
       </c>
       <c r="R27">
-        <v>0.363</v>
+        <v>0.278</v>
       </c>
       <c r="S27" t="s">
-        <v>43</v>
-      </c>
-      <c r="T27">
-        <v>0.2591</v>
-      </c>
-      <c r="U27">
-        <v>0.2289</v>
+        <v>89</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>0.2148</v>
+        <v>0.2347</v>
       </c>
       <c r="X27">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y27">
-        <v>1.0343</v>
+        <v>1.0021</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3265,22 +3379,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>5.44</v>
+        <v>3.38</v>
       </c>
       <c r="AE27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF27">
-        <v>0.1797</v>
+        <v>0.1688</v>
       </c>
       <c r="AG27">
-        <v>1.2178</v>
+        <v>1.0368</v>
       </c>
       <c r="AH27">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AM27">
-        <v>5.66</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3288,7 +3402,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F28" t="s">
         <v>88</v>
@@ -3297,10 +3411,10 @@
         <v>823178</v>
       </c>
       <c r="H28" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I28">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3312,37 +3426,43 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0.1688</v>
+        <v>0.2061</v>
       </c>
       <c r="N28">
         <v>4</v>
       </c>
       <c r="O28">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="P28">
-        <v>4.62</v>
+        <v>4.01</v>
       </c>
       <c r="Q28">
-        <v>0.1688</v>
+        <v>0.2024</v>
       </c>
       <c r="R28">
-        <v>0.278</v>
+        <v>0.296</v>
       </c>
       <c r="S28" t="s">
-        <v>89</v>
+        <v>43</v>
+      </c>
+      <c r="T28">
+        <v>0.1731</v>
+      </c>
+      <c r="U28">
+        <v>0.1743</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>0.2347</v>
+        <v>0.1969</v>
       </c>
       <c r="X28">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="Y28">
-        <v>1.0043</v>
+        <v>0.9439</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3351,22 +3471,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>3.38</v>
+        <v>3.27</v>
       </c>
       <c r="AE28" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF28">
-        <v>0.1688</v>
+        <v>0.205</v>
       </c>
       <c r="AG28">
-        <v>1.0368</v>
+        <v>0.8146</v>
       </c>
       <c r="AH28">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AM28">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3374,67 +3494,34 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="C29">
+        <v>3.5</v>
+      </c>
+      <c r="D29">
+        <v>-170</v>
+      </c>
+      <c r="E29">
+        <v>132</v>
       </c>
       <c r="F29" t="s">
-        <v>88</v>
-      </c>
-      <c r="G29">
-        <v>823178</v>
+        <v>57</v>
+      </c>
+      <c r="G29" t="s">
+        <v>44</v>
       </c>
       <c r="H29" t="s">
-        <v>42</v>
-      </c>
-      <c r="I29">
-        <v>5.2</v>
-      </c>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0.2061</v>
-      </c>
-      <c r="N29">
         <v>4</v>
       </c>
-      <c r="O29">
-        <v>84</v>
-      </c>
-      <c r="P29">
-        <v>4.01</v>
-      </c>
-      <c r="Q29">
-        <v>0.2024</v>
-      </c>
-      <c r="R29">
-        <v>0.296</v>
-      </c>
       <c r="S29" t="s">
-        <v>43</v>
-      </c>
-      <c r="T29">
-        <v>0.1731</v>
-      </c>
-      <c r="U29">
-        <v>0.1743</v>
-      </c>
-      <c r="V29">
-        <v>9</v>
-      </c>
-      <c r="W29">
-        <v>0.1969</v>
-      </c>
-      <c r="X29">
-        <v>0.2128</v>
-      </c>
-      <c r="Y29">
-        <v>0.9436</v>
+        <v>44</v>
+      </c>
+      <c r="V29" t="s">
+        <v>44</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3442,23 +3529,52 @@
       <c r="AC29" t="s">
         <v>44</v>
       </c>
-      <c r="AD29">
-        <v>3.26</v>
-      </c>
       <c r="AE29" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF29">
-        <v>0.205</v>
-      </c>
-      <c r="AG29">
-        <v>0.8134</v>
-      </c>
-      <c r="AH29">
-        <v>0.22</v>
-      </c>
-      <c r="AM29">
-        <v>3.48</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30">
+        <v>4.5</v>
+      </c>
+      <c r="D30">
+        <v>-162</v>
+      </c>
+      <c r="E30">
+        <v>126</v>
+      </c>
+      <c r="F30" t="s">
+        <v>83</v>
+      </c>
+      <c r="G30" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" t="s">
+        <v>44</v>
+      </c>
+      <c r="L30">
+        <v>3</v>
+      </c>
+      <c r="S30" t="s">
+        <v>44</v>
+      </c>
+      <c r="V30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-28.xlsx
+++ b/data/k-props/2026-08-28.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="93">
   <si>
     <t>date</t>
   </si>
@@ -133,154 +133,154 @@
     <t>08/28/2026</t>
   </si>
   <si>
+    <t>Rhett Lowder</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>David Peterson</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Tarik Skubal</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Detroit Tigers</t>
+  </si>
+  <si>
+    <t>Drew Anderson</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Eury Pérez</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Washington Nationals</t>
+  </si>
+  <si>
+    <t>Michael Wacha</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Tanner Bibee</t>
+  </si>
+  <si>
+    <t>Hunter Brown</t>
+  </si>
+  <si>
+    <t>Houston Astros @ New York Mets</t>
+  </si>
+  <si>
+    <t>Christian Scott</t>
+  </si>
+  <si>
+    <t>Casey Mize</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Shane McClanahan</t>
+  </si>
+  <si>
+    <t>Emerson Hancock</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>Dylan Cease</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Tomoyuki Sugano</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Grant Holmes</t>
+  </si>
+  <si>
+    <t>Patrick Sandoval</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Cam Schlittler</t>
+  </si>
+  <si>
+    <t>Cody Bradford</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Logan Henderson</t>
+  </si>
+  <si>
+    <t>Luis Castillo</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Dean Kremer</t>
+  </si>
+  <si>
+    <t>Jared Jones</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ St. Louis Cardinals</t>
+  </si>
+  <si>
+    <t>Andrew Painter</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Reid Detmers</t>
+  </si>
+  <si>
+    <t>Brandon Young</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Athletics</t>
+  </si>
+  <si>
     <t>Jacob Lopez</t>
   </si>
   <si>
-    <t>Baltimore Orioles @ Athletics</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Brandon Young</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Rhett Lowder</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t>David Peterson</t>
-  </si>
-  <si>
-    <t>Tarik Skubal</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Detroit Tigers</t>
-  </si>
-  <si>
-    <t>Drew Anderson</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Eury Pérez</t>
-  </si>
-  <si>
-    <t>Miami Marlins @ Washington Nationals</t>
-  </si>
-  <si>
-    <t>Michael Wacha</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Tanner Bibee</t>
-  </si>
-  <si>
-    <t>Hunter Brown</t>
-  </si>
-  <si>
-    <t>Houston Astros @ New York Mets</t>
-  </si>
-  <si>
-    <t>Christian Scott</t>
-  </si>
-  <si>
-    <t>Casey Mize</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Shane McClanahan</t>
-  </si>
-  <si>
-    <t>Dylan Cease</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Tomoyuki Sugano</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Grant Holmes</t>
-  </si>
-  <si>
-    <t>Patrick Sandoval</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Cam Schlittler</t>
-  </si>
-  <si>
-    <t>Cody Bradford</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Logan Henderson</t>
-  </si>
-  <si>
-    <t>Luis Castillo</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Dean Kremer</t>
-  </si>
-  <si>
-    <t>Jared Jones</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ St. Louis Cardinals</t>
-  </si>
-  <si>
-    <t>Andrew Painter</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Reid Detmers</t>
-  </si>
-  <si>
     <t>Kohl Drake</t>
   </si>
   <si>
     <t>Arizona Diamondbacks @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>team_season_vs_hand</t>
   </si>
   <si>
     <t>Blade Tidwell</t>
@@ -670,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM30"/>
+  <dimension ref="A1:AM31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -803,25 +803,25 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D2">
-        <v>117</v>
+        <v>-140</v>
       </c>
       <c r="E2">
-        <v>-142</v>
+        <v>116</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>824960</v>
+        <v>824638</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -830,46 +830,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>0.2148</v>
+        <v>0.1764</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="P2">
         <v>4.46</v>
       </c>
       <c r="Q2">
-        <v>0.3162</v>
+        <v>0.1463</v>
       </c>
       <c r="R2">
-        <v>0.369</v>
+        <v>0.381</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2627</v>
+        <v>0.2076</v>
       </c>
       <c r="U2">
-        <v>0.2436</v>
+        <v>0.2062</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2586</v>
+        <v>0.216</v>
       </c>
       <c r="X2">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y2">
-        <v>1.0521</v>
+        <v>0.9439</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -878,22 +878,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>6.79</v>
+        <v>3.29</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.247</v>
+        <v>0.1649</v>
       </c>
       <c r="AG2">
-        <v>1.2363</v>
+        <v>0.9492</v>
       </c>
       <c r="AH2">
-        <v>-0.58</v>
+        <v>0.24</v>
       </c>
       <c r="AM2">
-        <v>6.21</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -907,22 +907,22 @@
         <v>4.5</v>
       </c>
       <c r="D3">
-        <v>123</v>
+        <v>-156</v>
       </c>
       <c r="E3">
-        <v>-142</v>
+        <v>122</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
       <c r="G3">
-        <v>824960</v>
+        <v>824638</v>
       </c>
       <c r="H3" t="s">
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -931,46 +931,46 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>0.1871</v>
+        <v>0.196</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="P3">
-        <v>4.29</v>
+        <v>4.51</v>
       </c>
       <c r="Q3">
-        <v>0.1667</v>
+        <v>0.25</v>
       </c>
       <c r="R3">
-        <v>0.363</v>
+        <v>0.383</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.2591</v>
+        <v>0.2592</v>
       </c>
       <c r="U3">
-        <v>0.2289</v>
+        <v>0.2661</v>
       </c>
       <c r="V3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2148</v>
+        <v>0.2487</v>
       </c>
       <c r="X3">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y3">
-        <v>1.0344</v>
+        <v>1.0713</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -979,22 +979,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>5.45</v>
+        <v>6.29</v>
       </c>
       <c r="AE3" t="s">
         <v>47</v>
       </c>
       <c r="AF3">
-        <v>0.1797</v>
+        <v>0.2167</v>
       </c>
       <c r="AG3">
-        <v>1.2197</v>
+        <v>1.1853</v>
       </c>
       <c r="AH3">
-        <v>0.24</v>
+        <v>-0.58</v>
       </c>
       <c r="AM3">
-        <v>5.69</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1005,25 +1005,25 @@
         <v>48</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D4">
-        <v>-140</v>
+        <v>-156</v>
       </c>
       <c r="E4">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F4" t="s">
         <v>49</v>
       </c>
       <c r="G4">
-        <v>824638</v>
+        <v>824231</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1035,43 +1035,43 @@
         <v>4</v>
       </c>
       <c r="M4">
-        <v>0.1736</v>
+        <v>0.3087</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P4">
-        <v>4.47</v>
+        <v>3.92</v>
       </c>
       <c r="Q4">
-        <v>0.144</v>
+        <v>0.2903</v>
       </c>
       <c r="R4">
-        <v>0.385</v>
+        <v>0.383</v>
       </c>
       <c r="S4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="T4">
-        <v>0.2076</v>
+        <v>0.2075</v>
       </c>
       <c r="U4">
-        <v>0.2062</v>
+        <v>0.2041</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2164</v>
+        <v>0.2272</v>
       </c>
       <c r="X4">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y4">
-        <v>0.9439</v>
+        <v>0.9941</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1080,22 +1080,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.34</v>
+        <v>6.73</v>
       </c>
       <c r="AE4" t="s">
         <v>47</v>
       </c>
       <c r="AF4">
-        <v>0.1622</v>
+        <v>0.3016</v>
       </c>
       <c r="AG4">
-        <v>0.977</v>
+        <v>0.9491</v>
       </c>
       <c r="AH4">
-        <v>0.24</v>
+        <v>-0.58</v>
       </c>
       <c r="AM4">
-        <v>3.58</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1103,28 +1103,28 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>4.5</v>
       </c>
       <c r="D5">
-        <v>-156</v>
+        <v>-103</v>
       </c>
       <c r="E5">
-        <v>122</v>
+        <v>-120</v>
       </c>
       <c r="F5" t="s">
         <v>49</v>
       </c>
       <c r="G5">
-        <v>824638</v>
+        <v>824231</v>
       </c>
       <c r="H5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I5">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1136,43 +1136,43 @@
         <v>4</v>
       </c>
       <c r="M5">
-        <v>0.1936</v>
+        <v>0.2615</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="P5">
-        <v>4.5</v>
+        <v>4.28</v>
       </c>
       <c r="Q5">
-        <v>0.2295</v>
+        <v>0.2143</v>
       </c>
       <c r="R5">
-        <v>0.379</v>
+        <v>0.296</v>
       </c>
       <c r="S5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2592</v>
+        <v>0.2088</v>
       </c>
       <c r="U5">
-        <v>0.2661</v>
+        <v>0.2039</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2487</v>
+        <v>0.2067</v>
       </c>
       <c r="X5">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y5">
-        <v>1.0713</v>
+        <v>0.971</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1181,22 +1181,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>6.18</v>
+        <v>4.09</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.2072</v>
+        <v>0.2475</v>
       </c>
       <c r="AG5">
-        <v>1.22</v>
+        <v>0.9547</v>
       </c>
       <c r="AH5">
-        <v>-0.58</v>
+        <v>0.24</v>
       </c>
       <c r="AM5">
-        <v>5.6</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1207,25 +1207,25 @@
         <v>52</v>
       </c>
       <c r="C6">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D6">
-        <v>-156</v>
+        <v>-111</v>
       </c>
       <c r="E6">
-        <v>130</v>
+        <v>-111</v>
       </c>
       <c r="F6" t="s">
         <v>53</v>
       </c>
       <c r="G6">
-        <v>824231</v>
+        <v>822691</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1237,43 +1237,43 @@
         <v>4</v>
       </c>
       <c r="M6">
-        <v>0.3087</v>
+        <v>0.266</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="P6">
-        <v>3.92</v>
+        <v>4.03</v>
       </c>
       <c r="Q6">
-        <v>0.2903</v>
+        <v>0.2672</v>
       </c>
       <c r="R6">
-        <v>0.383</v>
+        <v>0.367</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>0.1777</v>
+        <v>0.2243</v>
       </c>
       <c r="U6">
-        <v>0.1958</v>
+        <v>0.2297</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2272</v>
+        <v>0.2058</v>
       </c>
       <c r="X6">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y6">
-        <v>0.9799</v>
+        <v>1.0228</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1282,22 +1282,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>5.85</v>
+        <v>6.26</v>
       </c>
       <c r="AE6" t="s">
         <v>47</v>
       </c>
       <c r="AF6">
-        <v>0.3016</v>
+        <v>0.2665</v>
       </c>
       <c r="AG6">
-        <v>0.8366</v>
+        <v>1.0258</v>
       </c>
       <c r="AH6">
-        <v>0.24</v>
+        <v>-0.58</v>
       </c>
       <c r="AM6">
-        <v>6.09</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1311,22 +1311,22 @@
         <v>4.5</v>
       </c>
       <c r="D7">
-        <v>-103</v>
+        <v>127</v>
       </c>
       <c r="E7">
-        <v>-120</v>
+        <v>-160</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G7">
-        <v>824231</v>
+        <v>824396</v>
       </c>
       <c r="H7" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="I7">
-        <v>4.2</v>
+        <v>6.3</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1335,46 +1335,46 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>0.2615</v>
+        <v>0.1915</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="P7">
-        <v>4.28</v>
+        <v>4.05</v>
       </c>
       <c r="Q7">
-        <v>0.2143</v>
+        <v>0.1833</v>
       </c>
       <c r="R7">
-        <v>0.296</v>
+        <v>0.375</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
       </c>
       <c r="T7">
-        <v>0.2251</v>
+        <v>0.1795</v>
       </c>
       <c r="U7">
-        <v>0.1979</v>
+        <v>0.1771</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2067</v>
+        <v>0.2103</v>
       </c>
       <c r="X7">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y7">
-        <v>1.0009</v>
+        <v>0.88</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1383,22 +1383,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>4.68</v>
+        <v>3.44</v>
       </c>
       <c r="AE7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.2475</v>
+        <v>0.1884</v>
       </c>
       <c r="AG7">
-        <v>1.0596</v>
+        <v>0.8208</v>
       </c>
       <c r="AH7">
         <v>0.24</v>
       </c>
       <c r="AM7">
-        <v>4.92</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1409,25 +1409,25 @@
         <v>56</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D8">
-        <v>-111</v>
+        <v>-132</v>
       </c>
       <c r="E8">
-        <v>-111</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8">
-        <v>822691</v>
+        <v>824396</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1436,46 +1436,46 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>0.266</v>
+        <v>0.1931</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="P8">
-        <v>4.03</v>
+        <v>4.07</v>
       </c>
       <c r="Q8">
-        <v>0.2672</v>
+        <v>0.2047</v>
       </c>
       <c r="R8">
-        <v>0.367</v>
+        <v>0.388</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2282</v>
+        <v>0.1787</v>
       </c>
       <c r="U8">
-        <v>0.2321</v>
+        <v>0.1907</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2058</v>
+        <v>0.2075</v>
       </c>
       <c r="X8">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y8">
-        <v>1.0153</v>
+        <v>0.9542</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1484,22 +1484,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>6.51</v>
+        <v>3.63</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.2665</v>
+        <v>0.1976</v>
       </c>
       <c r="AG8">
-        <v>1.074</v>
+        <v>0.817</v>
       </c>
       <c r="AH8">
-        <v>-0.58</v>
+        <v>0.24</v>
       </c>
       <c r="AM8">
-        <v>5.93</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1507,28 +1507,28 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9">
+        <v>5.5</v>
+      </c>
+      <c r="D9">
+        <v>126</v>
+      </c>
+      <c r="E9">
+        <v>-135</v>
+      </c>
+      <c r="F9" t="s">
         <v>58</v>
       </c>
-      <c r="C9">
-        <v>4.5</v>
-      </c>
-      <c r="D9">
-        <v>127</v>
-      </c>
-      <c r="E9">
-        <v>-160</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
       <c r="G9">
-        <v>824396</v>
+        <v>823583</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1540,43 +1540,43 @@
         <v>3</v>
       </c>
       <c r="M9">
-        <v>0.1915</v>
+        <v>0.2413</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="P9">
-        <v>4.05</v>
+        <v>4.24</v>
       </c>
       <c r="Q9">
-        <v>0.1833</v>
+        <v>0.2261</v>
       </c>
       <c r="R9">
-        <v>0.375</v>
+        <v>0.365</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.1991</v>
+        <v>0.2115</v>
       </c>
       <c r="U9">
-        <v>0.1809</v>
+        <v>0.2117</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2103</v>
+        <v>0.2232</v>
       </c>
       <c r="X9">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y9">
-        <v>0.9478</v>
+        <v>0.947</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1585,22 +1585,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.24</v>
+        <v>4.86</v>
       </c>
       <c r="AE9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.1884</v>
+        <v>0.2357</v>
       </c>
       <c r="AG9">
-        <v>0.9371</v>
+        <v>0.9671</v>
       </c>
       <c r="AH9">
         <v>0.24</v>
       </c>
       <c r="AM9">
-        <v>4.48</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1608,28 +1608,28 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C10">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D10">
-        <v>-132</v>
+        <v>-149</v>
       </c>
       <c r="E10">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G10">
-        <v>824396</v>
+        <v>823583</v>
       </c>
       <c r="H10" t="s">
         <v>42</v>
       </c>
       <c r="I10">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1641,43 +1641,43 @@
         <v>3</v>
       </c>
       <c r="M10">
-        <v>0.1931</v>
+        <v>0.2846</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="P10">
-        <v>4.07</v>
+        <v>4.37</v>
       </c>
       <c r="Q10">
-        <v>0.2047</v>
+        <v>0.2773</v>
       </c>
       <c r="R10">
-        <v>0.388</v>
+        <v>0.373</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>0.173</v>
+        <v>0.225</v>
       </c>
       <c r="U10">
-        <v>0.1875</v>
+        <v>0.2075</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2075</v>
+        <v>0.2191</v>
       </c>
       <c r="X10">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y10">
-        <v>0.9621</v>
+        <v>0.9963</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1686,22 +1686,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.65</v>
+        <v>5.93</v>
       </c>
       <c r="AE10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.1976</v>
+        <v>0.2819</v>
       </c>
       <c r="AG10">
-        <v>0.8145</v>
+        <v>1.0291</v>
       </c>
       <c r="AH10">
         <v>0.24</v>
       </c>
       <c r="AM10">
-        <v>3.89</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1709,28 +1709,28 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11">
+        <v>3.5</v>
+      </c>
+      <c r="D11">
+        <v>-136</v>
+      </c>
+      <c r="E11">
+        <v>110</v>
+      </c>
+      <c r="F11" t="s">
         <v>61</v>
       </c>
-      <c r="C11">
-        <v>5.5</v>
-      </c>
-      <c r="D11">
-        <v>126</v>
-      </c>
-      <c r="E11">
-        <v>-135</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
       <c r="G11">
-        <v>823583</v>
+        <v>822935</v>
       </c>
       <c r="H11" t="s">
         <v>42</v>
       </c>
       <c r="I11">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1742,43 +1742,43 @@
         <v>3</v>
       </c>
       <c r="M11">
-        <v>0.2413</v>
+        <v>0.2257</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="P11">
-        <v>4.24</v>
+        <v>4.02</v>
       </c>
       <c r="Q11">
-        <v>0.2261</v>
+        <v>0.1287</v>
       </c>
       <c r="R11">
-        <v>0.365</v>
+        <v>0.336</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
       </c>
       <c r="T11">
-        <v>0.2352</v>
+        <v>0.1572</v>
       </c>
       <c r="U11">
-        <v>0.2305</v>
+        <v>0.1524</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2232</v>
+        <v>0.187</v>
       </c>
       <c r="X11">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y11">
-        <v>0.9924</v>
+        <v>0.88</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1787,22 +1787,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.83</v>
+        <v>2.57</v>
       </c>
       <c r="AE11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.2357</v>
+        <v>0.1931</v>
       </c>
       <c r="AG11">
-        <v>1.1069</v>
+        <v>0.7191</v>
       </c>
       <c r="AH11">
         <v>0.24</v>
       </c>
       <c r="AM11">
-        <v>6.07</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1810,28 +1810,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D12">
-        <v>-149</v>
+        <v>-104</v>
       </c>
       <c r="E12">
-        <v>140</v>
+        <v>-122</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12">
-        <v>823583</v>
+        <v>822935</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
       </c>
       <c r="I12">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1843,43 +1843,43 @@
         <v>3</v>
       </c>
       <c r="M12">
-        <v>0.2846</v>
+        <v>0.2235</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="P12">
-        <v>4.37</v>
+        <v>4.13</v>
       </c>
       <c r="Q12">
-        <v>0.2773</v>
+        <v>0.191</v>
       </c>
       <c r="R12">
-        <v>0.373</v>
+        <v>0.308</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
       </c>
       <c r="T12">
-        <v>0.2264</v>
+        <v>0.1994</v>
       </c>
       <c r="U12">
-        <v>0.2164</v>
+        <v>0.1938</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2191</v>
+        <v>0.2232</v>
       </c>
       <c r="X12">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y12">
-        <v>1.0154</v>
+        <v>1.028</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1888,22 +1888,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>6.26</v>
+        <v>4.03</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.2819</v>
+        <v>0.2135</v>
       </c>
       <c r="AG12">
-        <v>1.0657</v>
+        <v>0.9118</v>
       </c>
       <c r="AH12">
-        <v>-0.58</v>
+        <v>0.24</v>
       </c>
       <c r="AM12">
-        <v>5.68</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1911,28 +1911,28 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13">
         <v>3.5</v>
       </c>
       <c r="D13">
-        <v>-136</v>
+        <v>-122</v>
       </c>
       <c r="E13">
-        <v>110</v>
+        <v>-104</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G13">
-        <v>822935</v>
+        <v>822769</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1941,46 +1941,46 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>0.2257</v>
+        <v>0.2302</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="P13">
-        <v>4.02</v>
+        <v>4.06</v>
       </c>
       <c r="Q13">
-        <v>0.1287</v>
+        <v>0.2171</v>
       </c>
       <c r="R13">
-        <v>0.336</v>
+        <v>0.392</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
       </c>
       <c r="T13">
-        <v>0.1603</v>
+        <v>0.1979</v>
       </c>
       <c r="U13">
-        <v>0.1542</v>
+        <v>0.1847</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.187</v>
+        <v>0.1885</v>
       </c>
       <c r="X13">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y13">
-        <v>0.9142</v>
+        <v>0.9887</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1989,22 +1989,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>2.8</v>
+        <v>4.56</v>
       </c>
       <c r="AE13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.1931</v>
+        <v>0.225</v>
       </c>
       <c r="AG13">
-        <v>0.7544</v>
+        <v>0.9053</v>
       </c>
       <c r="AH13">
         <v>0.24</v>
       </c>
       <c r="AM13">
-        <v>3.04</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2012,28 +2012,28 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C14">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="D14">
-        <v>-104</v>
+        <v>-120</v>
       </c>
       <c r="E14">
-        <v>-122</v>
+        <v>102</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G14">
-        <v>822935</v>
+        <v>822769</v>
       </c>
       <c r="H14" t="s">
         <v>42</v>
       </c>
       <c r="I14">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2042,46 +2042,46 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>0.2235</v>
+        <v>0.361</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="P14">
-        <v>4.13</v>
+        <v>4.01</v>
       </c>
       <c r="Q14">
-        <v>0.191</v>
+        <v>0.3443</v>
       </c>
       <c r="R14">
-        <v>0.308</v>
+        <v>0.379</v>
       </c>
       <c r="S14" t="s">
         <v>43</v>
       </c>
       <c r="T14">
-        <v>0.1879</v>
+        <v>0.2596</v>
       </c>
       <c r="U14">
-        <v>0.1901</v>
+        <v>0.2326</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2232</v>
+        <v>0.2256</v>
       </c>
       <c r="X14">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y14">
-        <v>0.9895</v>
+        <v>0.9451</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2090,22 +2090,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>3.76</v>
+        <v>9.6</v>
       </c>
       <c r="AE14" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="AF14">
-        <v>0.2135</v>
+        <v>0.3546</v>
       </c>
       <c r="AG14">
-        <v>0.8844</v>
+        <v>1.1873</v>
       </c>
       <c r="AH14">
-        <v>0.24</v>
+        <v>-0.95</v>
       </c>
       <c r="AM14">
-        <v>4</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2115,17 +2115,26 @@
       <c r="B15" t="s">
         <v>67</v>
       </c>
+      <c r="C15">
+        <v>2.5</v>
+      </c>
+      <c r="D15">
+        <v>-186</v>
+      </c>
+      <c r="E15">
+        <v>145</v>
+      </c>
       <c r="F15" t="s">
         <v>68</v>
       </c>
       <c r="G15">
-        <v>822769</v>
+        <v>824877</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2134,46 +2143,46 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15">
-        <v>0.361</v>
+        <v>0.1376</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="P15">
-        <v>4.01</v>
+        <v>4.24</v>
       </c>
       <c r="Q15">
-        <v>0.3443</v>
+        <v>0.1351</v>
       </c>
       <c r="R15">
-        <v>0.379</v>
+        <v>0.357</v>
       </c>
       <c r="S15" t="s">
         <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2187</v>
+        <v>0.2378</v>
       </c>
       <c r="U15">
-        <v>0.2249</v>
+        <v>0.2052</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2256</v>
+        <v>0.2212</v>
       </c>
       <c r="X15">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y15">
-        <v>0.9889</v>
+        <v>0.9527</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2182,22 +2191,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>8.71</v>
+        <v>3.18</v>
       </c>
       <c r="AE15" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.3546</v>
+        <v>0.1367</v>
       </c>
       <c r="AG15">
-        <v>1.0294</v>
+        <v>1.0873</v>
       </c>
       <c r="AH15">
-        <v>-0.95</v>
+        <v>0.24</v>
       </c>
       <c r="AM15">
-        <v>7.76</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2205,19 +2214,19 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C16">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="D16">
-        <v>-186</v>
+        <v>-111</v>
       </c>
       <c r="E16">
-        <v>145</v>
+        <v>-115</v>
       </c>
       <c r="F16" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G16">
         <v>824877</v>
@@ -2226,7 +2235,7 @@
         <v>42</v>
       </c>
       <c r="I16">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2235,46 +2244,46 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16">
-        <v>0.1376</v>
+        <v>0.189</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="P16">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
       <c r="Q16">
-        <v>0.1351</v>
+        <v>0.1589</v>
       </c>
       <c r="R16">
-        <v>0.357</v>
+        <v>0.349</v>
       </c>
       <c r="S16" t="s">
         <v>43</v>
       </c>
       <c r="T16">
-        <v>0.2292</v>
+        <v>0.2612</v>
       </c>
       <c r="U16">
-        <v>0.226</v>
+        <v>0.2353</v>
       </c>
       <c r="V16">
         <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2212</v>
+        <v>0.2184</v>
       </c>
       <c r="X16">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y16">
-        <v>0.9945</v>
+        <v>1.0808</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2283,22 +2292,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>3.29</v>
+        <v>4.92</v>
       </c>
       <c r="AE16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF16">
-        <v>0.1367</v>
+        <v>0.1785</v>
       </c>
       <c r="AG16">
-        <v>1.0789</v>
+        <v>1.1944</v>
       </c>
       <c r="AH16">
         <v>0.24</v>
       </c>
       <c r="AM16">
-        <v>3.53</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2306,22 +2315,22 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C17">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D17">
-        <v>-111</v>
+        <v>-119</v>
       </c>
       <c r="E17">
-        <v>-115</v>
+        <v>-104</v>
       </c>
       <c r="F17" t="s">
         <v>71</v>
       </c>
       <c r="G17">
-        <v>824877</v>
+        <v>823504</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
@@ -2336,46 +2345,46 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>0.189</v>
+        <v>0.2228</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="P17">
-        <v>4.28</v>
+        <v>4.64</v>
       </c>
       <c r="Q17">
-        <v>0.1589</v>
+        <v>0.2333</v>
       </c>
       <c r="R17">
-        <v>0.349</v>
+        <v>0.375</v>
       </c>
       <c r="S17" t="s">
         <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2137</v>
+        <v>0.2496</v>
       </c>
       <c r="U17">
-        <v>0.2098</v>
+        <v>0.2617</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2184</v>
+        <v>0.2479</v>
       </c>
       <c r="X17">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y17">
-        <v>1.0239</v>
+        <v>0.9905</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2384,22 +2393,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>3.92</v>
+        <v>5.9</v>
       </c>
       <c r="AE17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF17">
-        <v>0.1785</v>
+        <v>0.2268</v>
       </c>
       <c r="AG17">
-        <v>1.0061</v>
+        <v>1.1413</v>
       </c>
       <c r="AH17">
         <v>0.24</v>
       </c>
       <c r="AM17">
-        <v>4.16</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2407,19 +2416,19 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D18">
-        <v>-119</v>
+        <v>-130</v>
       </c>
       <c r="E18">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G18">
         <v>823504</v>
@@ -2428,7 +2437,7 @@
         <v>42</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2440,43 +2449,43 @@
         <v>4</v>
       </c>
       <c r="M18">
-        <v>0.2228</v>
+        <v>0.3078</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="P18">
-        <v>4.64</v>
+        <v>3.97</v>
       </c>
       <c r="Q18">
-        <v>0.2333</v>
+        <v>0.3214</v>
       </c>
       <c r="R18">
-        <v>0.375</v>
+        <v>0.359</v>
       </c>
       <c r="S18" t="s">
         <v>43</v>
       </c>
       <c r="T18">
-        <v>0.2361</v>
+        <v>0.1768</v>
       </c>
       <c r="U18">
-        <v>0.2453</v>
+        <v>0.1867</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2479</v>
+        <v>0.2131</v>
       </c>
       <c r="X18">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y18">
-        <v>0.984</v>
+        <v>1.0264</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2485,22 +2494,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>5.7</v>
+        <v>6.03</v>
       </c>
       <c r="AE18" t="s">
         <v>47</v>
       </c>
       <c r="AF18">
-        <v>0.2268</v>
+        <v>0.3127</v>
       </c>
       <c r="AG18">
-        <v>1.1114</v>
+        <v>0.8084</v>
       </c>
       <c r="AH18">
-        <v>0.24</v>
+        <v>-0.58</v>
       </c>
       <c r="AM18">
-        <v>5.94</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2508,28 +2517,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C19">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D19">
-        <v>-130</v>
+        <v>-140</v>
       </c>
       <c r="E19">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="F19" t="s">
         <v>74</v>
       </c>
       <c r="G19">
-        <v>823504</v>
+        <v>823744</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2538,46 +2547,46 @@
         <v>0</v>
       </c>
       <c r="L19">
+        <v>3</v>
+      </c>
+      <c r="M19">
+        <v>0.1494</v>
+      </c>
+      <c r="N19">
         <v>4</v>
       </c>
-      <c r="M19">
-        <v>0.3078</v>
-      </c>
-      <c r="N19">
-        <v>5</v>
-      </c>
       <c r="O19">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="P19">
-        <v>3.97</v>
+        <v>4.21</v>
       </c>
       <c r="Q19">
-        <v>0.3214</v>
+        <v>0.1494</v>
       </c>
       <c r="R19">
-        <v>0.359</v>
+        <v>0.303</v>
       </c>
       <c r="S19" t="s">
         <v>43</v>
       </c>
       <c r="T19">
-        <v>0.188</v>
+        <v>0.216</v>
       </c>
       <c r="U19">
-        <v>0.1848</v>
+        <v>0.2169</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2131</v>
+        <v>0.2175</v>
       </c>
       <c r="X19">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y19">
-        <v>0.9872</v>
+        <v>1.0232</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2586,22 +2595,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>6.34</v>
+        <v>3.29</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.3127</v>
+        <v>0.1494</v>
       </c>
       <c r="AG19">
-        <v>0.885</v>
+        <v>0.9879</v>
       </c>
       <c r="AH19">
-        <v>-0.58</v>
+        <v>0.24</v>
       </c>
       <c r="AM19">
-        <v>5.76</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2609,19 +2618,19 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C20">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D20">
-        <v>-140</v>
+        <v>-113</v>
       </c>
       <c r="E20">
-        <v>115</v>
+        <v>-111</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G20">
         <v>823744</v>
@@ -2630,7 +2639,7 @@
         <v>42</v>
       </c>
       <c r="I20">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2642,43 +2651,43 @@
         <v>3</v>
       </c>
       <c r="M20">
-        <v>0.1494</v>
+        <v>0.2992</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="P20">
-        <v>4.21</v>
+        <v>3.81</v>
       </c>
       <c r="Q20">
-        <v>0.1494</v>
+        <v>0.2759</v>
       </c>
       <c r="R20">
-        <v>0.303</v>
+        <v>0.367</v>
       </c>
       <c r="S20" t="s">
         <v>43</v>
       </c>
       <c r="T20">
-        <v>0.216</v>
+        <v>0.2505</v>
       </c>
       <c r="U20">
-        <v>0.2169</v>
+        <v>0.2364</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2175</v>
+        <v>0.223</v>
       </c>
       <c r="X20">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y20">
-        <v>1.0116</v>
+        <v>1.0904</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2687,22 +2696,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>3.34</v>
+        <v>7.37</v>
       </c>
       <c r="AE20" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="AF20">
-        <v>0.1494</v>
+        <v>0.2907</v>
       </c>
       <c r="AG20">
-        <v>1.0168</v>
+        <v>1.1454</v>
       </c>
       <c r="AH20">
-        <v>0.24</v>
+        <v>-0.95</v>
       </c>
       <c r="AM20">
-        <v>3.58</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2710,28 +2719,28 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C21">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D21">
-        <v>-113</v>
+        <v>-170</v>
       </c>
       <c r="E21">
-        <v>-111</v>
+        <v>134</v>
       </c>
       <c r="F21" t="s">
         <v>77</v>
       </c>
       <c r="G21">
-        <v>823744</v>
+        <v>823666</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
       </c>
       <c r="I21">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2740,46 +2749,46 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M21">
-        <v>0.2992</v>
+        <v>0.2</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="P21">
-        <v>3.81</v>
+        <v>4.45</v>
       </c>
       <c r="Q21">
-        <v>0.2759</v>
+        <v>0.1944</v>
       </c>
       <c r="R21">
-        <v>0.367</v>
+        <v>0.351</v>
       </c>
       <c r="S21" t="s">
         <v>43</v>
       </c>
       <c r="T21">
-        <v>0.2247</v>
+        <v>0.1851</v>
       </c>
       <c r="U21">
-        <v>0.236</v>
+        <v>0.1819</v>
       </c>
       <c r="V21">
         <v>8</v>
       </c>
       <c r="W21">
-        <v>0.223</v>
+        <v>0.2077</v>
       </c>
       <c r="X21">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y21">
-        <v>1.0375</v>
+        <v>0.9332</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2788,22 +2797,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>6.48</v>
+        <v>3.54</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
       </c>
       <c r="AF21">
-        <v>0.2907</v>
+        <v>0.1981</v>
       </c>
       <c r="AG21">
-        <v>1.0578</v>
+        <v>0.8464</v>
       </c>
       <c r="AH21">
-        <v>-0.58</v>
+        <v>0.24</v>
       </c>
       <c r="AM21">
-        <v>5.9</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2811,19 +2820,19 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C22">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D22">
-        <v>-170</v>
+        <v>110</v>
       </c>
       <c r="E22">
-        <v>134</v>
+        <v>-138</v>
       </c>
       <c r="F22" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G22">
         <v>823666</v>
@@ -2832,7 +2841,7 @@
         <v>42</v>
       </c>
       <c r="I22">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2844,43 +2853,43 @@
         <v>2</v>
       </c>
       <c r="M22">
-        <v>0.2</v>
+        <v>0.2427</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P22">
-        <v>4.45</v>
+        <v>4.07</v>
       </c>
       <c r="Q22">
-        <v>0.1944</v>
+        <v>0.2202</v>
       </c>
       <c r="R22">
-        <v>0.351</v>
+        <v>0.353</v>
       </c>
       <c r="S22" t="s">
         <v>43</v>
       </c>
       <c r="T22">
-        <v>0.1887</v>
+        <v>0.246</v>
       </c>
       <c r="U22">
-        <v>0.1857</v>
+        <v>0.2525</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2077</v>
+        <v>0.2369</v>
       </c>
       <c r="X22">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y22">
-        <v>0.9752</v>
+        <v>1.0791</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2889,22 +2898,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>3.88</v>
+        <v>6.19</v>
       </c>
       <c r="AE22" t="s">
         <v>47</v>
       </c>
       <c r="AF22">
-        <v>0.1981</v>
+        <v>0.2347</v>
       </c>
       <c r="AG22">
-        <v>0.8884</v>
+        <v>1.1249</v>
       </c>
       <c r="AH22">
-        <v>0.24</v>
+        <v>-0.58</v>
       </c>
       <c r="AM22">
-        <v>4.12</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2912,28 +2921,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C23">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D23">
-        <v>110</v>
+        <v>-130</v>
       </c>
       <c r="E23">
-        <v>-138</v>
+        <v>115</v>
       </c>
       <c r="F23" t="s">
         <v>80</v>
       </c>
       <c r="G23">
-        <v>823666</v>
+        <v>823013</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2942,46 +2951,46 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M23">
-        <v>0.2427</v>
+        <v>0.2664</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P23">
-        <v>4.07</v>
+        <v>4.25</v>
       </c>
       <c r="Q23">
-        <v>0.2202</v>
+        <v>0.2286</v>
       </c>
       <c r="R23">
-        <v>0.353</v>
+        <v>0.344</v>
       </c>
       <c r="S23" t="s">
         <v>43</v>
       </c>
       <c r="T23">
-        <v>0.2261</v>
+        <v>0.2554</v>
       </c>
       <c r="U23">
-        <v>0.248</v>
+        <v>0.2107</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2369</v>
+        <v>0.2155</v>
       </c>
       <c r="X23">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y23">
-        <v>1.0341</v>
+        <v>0.911</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2990,22 +2999,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>5.61</v>
+        <v>5.19</v>
       </c>
       <c r="AE23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.2347</v>
+        <v>0.2534</v>
       </c>
       <c r="AG23">
-        <v>1.0644</v>
+        <v>1.1678</v>
       </c>
       <c r="AH23">
         <v>0.24</v>
       </c>
       <c r="AM23">
-        <v>5.85</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3013,28 +3022,28 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24">
+        <v>5.5</v>
+      </c>
+      <c r="D24">
+        <v>122</v>
+      </c>
+      <c r="E24">
+        <v>-156</v>
+      </c>
+      <c r="F24" t="s">
         <v>82</v>
       </c>
-      <c r="C24">
-        <v>4.5</v>
-      </c>
-      <c r="D24">
-        <v>-130</v>
-      </c>
-      <c r="E24">
-        <v>115</v>
-      </c>
-      <c r="F24" t="s">
-        <v>83</v>
-      </c>
       <c r="G24">
-        <v>823013</v>
+        <v>823985</v>
       </c>
       <c r="H24" t="s">
         <v>42</v>
       </c>
       <c r="I24">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -3043,46 +3052,46 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M24">
-        <v>0.2664</v>
+        <v>0.1927</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="P24">
-        <v>4.25</v>
+        <v>4.44</v>
       </c>
       <c r="Q24">
-        <v>0.2286</v>
+        <v>0.2342</v>
       </c>
       <c r="R24">
-        <v>0.344</v>
+        <v>0.357</v>
       </c>
       <c r="S24" t="s">
         <v>43</v>
       </c>
       <c r="T24">
-        <v>0.2404</v>
+        <v>0.2386</v>
       </c>
       <c r="U24">
-        <v>0.2045</v>
+        <v>0.2532</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>0.2155</v>
+        <v>0.252</v>
       </c>
       <c r="X24">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y24">
-        <v>0.9549</v>
+        <v>1.0671</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -3091,22 +3100,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>5.28</v>
+        <v>5.2</v>
       </c>
       <c r="AE24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF24">
-        <v>0.2534</v>
+        <v>0.2075</v>
       </c>
       <c r="AG24">
-        <v>1.1318</v>
+        <v>1.0912</v>
       </c>
       <c r="AH24">
         <v>0.24</v>
       </c>
       <c r="AM24">
-        <v>5.52</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3114,19 +3123,19 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C25">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D25">
-        <v>122</v>
+        <v>-125</v>
       </c>
       <c r="E25">
-        <v>-156</v>
+        <v>-102</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G25">
         <v>823985</v>
@@ -3135,7 +3144,7 @@
         <v>42</v>
       </c>
       <c r="I25">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -3147,43 +3156,43 @@
         <v>2</v>
       </c>
       <c r="M25">
-        <v>0.1927</v>
+        <v>0.2852</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P25">
-        <v>4.44</v>
+        <v>4.05</v>
       </c>
       <c r="Q25">
-        <v>0.2342</v>
+        <v>0.3273</v>
       </c>
       <c r="R25">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="S25" t="s">
         <v>43</v>
       </c>
       <c r="T25">
-        <v>0.2562</v>
+        <v>0.171</v>
       </c>
       <c r="U25">
-        <v>0.2478</v>
+        <v>0.1638</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.252</v>
+        <v>0.2269</v>
       </c>
       <c r="X25">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y25">
-        <v>1.0402</v>
+        <v>0.9462</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3192,22 +3201,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>5.6</v>
+        <v>5.15</v>
       </c>
       <c r="AE25" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF25">
-        <v>0.2075</v>
+        <v>0.3002</v>
       </c>
       <c r="AG25">
-        <v>1.2061</v>
+        <v>0.7821</v>
       </c>
       <c r="AH25">
         <v>0.24</v>
       </c>
       <c r="AM25">
-        <v>5.84</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3215,28 +3224,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C26">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D26">
-        <v>-125</v>
+        <v>123</v>
       </c>
       <c r="E26">
-        <v>-102</v>
+        <v>-142</v>
       </c>
       <c r="F26" t="s">
         <v>85</v>
       </c>
       <c r="G26">
-        <v>823985</v>
+        <v>824960</v>
       </c>
       <c r="H26" t="s">
         <v>42</v>
       </c>
       <c r="I26">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3245,46 +3254,46 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>0.2852</v>
+        <v>0.1871</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="P26">
-        <v>4.05</v>
+        <v>4.29</v>
       </c>
       <c r="Q26">
-        <v>0.3273</v>
+        <v>0.1667</v>
       </c>
       <c r="R26">
-        <v>0.355</v>
+        <v>0.363</v>
       </c>
       <c r="S26" t="s">
         <v>43</v>
       </c>
       <c r="T26">
-        <v>0.1526</v>
+        <v>0.2094</v>
       </c>
       <c r="U26">
-        <v>0.1542</v>
+        <v>0.2074</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2269</v>
+        <v>0.2148</v>
       </c>
       <c r="X26">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y26">
-        <v>0.9584</v>
+        <v>1.0058</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3293,22 +3302,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>4.79</v>
+        <v>4.16</v>
       </c>
       <c r="AE26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF26">
-        <v>0.3002</v>
+        <v>0.1797</v>
       </c>
       <c r="AG26">
-        <v>0.7183</v>
+        <v>0.9577</v>
       </c>
       <c r="AH26">
         <v>0.24</v>
       </c>
       <c r="AM26">
-        <v>5.03</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3316,61 +3325,76 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27">
+        <v>6.5</v>
+      </c>
+      <c r="D27">
+        <v>117</v>
+      </c>
+      <c r="E27">
+        <v>-142</v>
+      </c>
+      <c r="F27" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27">
+        <v>824960</v>
+      </c>
+      <c r="H27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I27">
+        <v>4.7</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>5</v>
+      </c>
+      <c r="M27">
+        <v>0.2148</v>
+      </c>
+      <c r="N27">
+        <v>5</v>
+      </c>
+      <c r="O27">
+        <v>117</v>
+      </c>
+      <c r="P27">
+        <v>4.46</v>
+      </c>
+      <c r="Q27">
+        <v>0.3162</v>
+      </c>
+      <c r="R27">
+        <v>0.369</v>
+      </c>
+      <c r="S27" t="s">
         <v>87</v>
       </c>
-      <c r="F27" t="s">
-        <v>88</v>
-      </c>
-      <c r="G27">
-        <v>823178</v>
-      </c>
-      <c r="H27" t="s">
-        <v>55</v>
-      </c>
-      <c r="I27">
-        <v>4.2</v>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>0.1688</v>
-      </c>
-      <c r="N27">
-        <v>4</v>
-      </c>
-      <c r="O27">
-        <v>77</v>
-      </c>
-      <c r="P27">
-        <v>4.62</v>
-      </c>
-      <c r="Q27">
-        <v>0.1688</v>
-      </c>
-      <c r="R27">
-        <v>0.278</v>
-      </c>
-      <c r="S27" t="s">
-        <v>89</v>
+      <c r="T27">
+        <v>0.2627</v>
+      </c>
+      <c r="U27">
+        <v>0.2436</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2347</v>
+        <v>0.2586</v>
       </c>
       <c r="X27">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y27">
-        <v>1.0021</v>
+        <v>1.0521</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3379,22 +3403,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>3.38</v>
+        <v>6.6</v>
       </c>
       <c r="AE27" t="s">
         <v>47</v>
       </c>
       <c r="AF27">
-        <v>0.1688</v>
+        <v>0.247</v>
       </c>
       <c r="AG27">
-        <v>1.0368</v>
+        <v>1.2012</v>
       </c>
       <c r="AH27">
-        <v>0.24</v>
+        <v>-0.58</v>
       </c>
       <c r="AM27">
-        <v>3.62</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3402,19 +3426,19 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G28">
         <v>823178</v>
       </c>
       <c r="H28" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I28">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3426,43 +3450,43 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0.2061</v>
+        <v>0.1688</v>
       </c>
       <c r="N28">
         <v>4</v>
       </c>
       <c r="O28">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="P28">
-        <v>4.01</v>
+        <v>4.62</v>
       </c>
       <c r="Q28">
-        <v>0.2024</v>
+        <v>0.1688</v>
       </c>
       <c r="R28">
-        <v>0.296</v>
+        <v>0.278</v>
       </c>
       <c r="S28" t="s">
         <v>43</v>
       </c>
       <c r="T28">
-        <v>0.1731</v>
+        <v>0.2345</v>
       </c>
       <c r="U28">
-        <v>0.1743</v>
+        <v>0.2152</v>
       </c>
       <c r="V28">
         <v>9</v>
       </c>
       <c r="W28">
-        <v>0.1969</v>
+        <v>0.2347</v>
       </c>
       <c r="X28">
-        <v>0.2124</v>
+        <v>0.2187</v>
       </c>
       <c r="Y28">
-        <v>0.9439</v>
+        <v>1.0126</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3471,22 +3495,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>3.27</v>
+        <v>3.53</v>
       </c>
       <c r="AE28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF28">
-        <v>0.205</v>
+        <v>0.1688</v>
       </c>
       <c r="AG28">
-        <v>0.8146</v>
+        <v>1.0724</v>
       </c>
       <c r="AH28">
         <v>0.24</v>
       </c>
       <c r="AM28">
-        <v>3.51</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3494,34 +3518,67 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29">
-        <v>3.5</v>
-      </c>
-      <c r="D29">
-        <v>-170</v>
-      </c>
-      <c r="E29">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="F29" t="s">
-        <v>57</v>
-      </c>
-      <c r="G29" t="s">
-        <v>44</v>
+        <v>89</v>
+      </c>
+      <c r="G29">
+        <v>823178</v>
       </c>
       <c r="H29" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I29">
+        <v>5.2</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
       </c>
       <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0.2061</v>
+      </c>
+      <c r="N29">
         <v>4</v>
       </c>
+      <c r="O29">
+        <v>84</v>
+      </c>
+      <c r="P29">
+        <v>4.01</v>
+      </c>
+      <c r="Q29">
+        <v>0.2024</v>
+      </c>
+      <c r="R29">
+        <v>0.296</v>
+      </c>
       <c r="S29" t="s">
-        <v>44</v>
-      </c>
-      <c r="V29" t="s">
-        <v>44</v>
+        <v>87</v>
+      </c>
+      <c r="T29">
+        <v>0.1731</v>
+      </c>
+      <c r="U29">
+        <v>0.1743</v>
+      </c>
+      <c r="V29">
+        <v>9</v>
+      </c>
+      <c r="W29">
+        <v>0.1969</v>
+      </c>
+      <c r="X29">
+        <v>0.2187</v>
+      </c>
+      <c r="Y29">
+        <v>0.9439</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3529,8 +3586,23 @@
       <c r="AC29" t="s">
         <v>44</v>
       </c>
+      <c r="AD29">
+        <v>3.17</v>
+      </c>
       <c r="AE29" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF29">
+        <v>0.205</v>
+      </c>
+      <c r="AG29">
+        <v>0.7915</v>
+      </c>
+      <c r="AH29">
+        <v>0.24</v>
+      </c>
+      <c r="AM29">
+        <v>3.41</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3538,42 +3610,86 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30">
+        <v>3.5</v>
+      </c>
+      <c r="D30">
+        <v>-170</v>
+      </c>
+      <c r="E30">
+        <v>132</v>
+      </c>
+      <c r="F30" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" t="s">
+        <v>44</v>
+      </c>
+      <c r="L30">
+        <v>4</v>
+      </c>
+      <c r="S30" t="s">
+        <v>44</v>
+      </c>
+      <c r="V30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" t="s">
         <v>92</v>
       </c>
-      <c r="C30">
+      <c r="C31">
         <v>4.5</v>
       </c>
-      <c r="D30">
+      <c r="D31">
         <v>-162</v>
       </c>
-      <c r="E30">
+      <c r="E31">
         <v>126</v>
       </c>
-      <c r="F30" t="s">
-        <v>83</v>
-      </c>
-      <c r="G30" t="s">
-        <v>44</v>
-      </c>
-      <c r="H30" t="s">
-        <v>44</v>
-      </c>
-      <c r="L30">
+      <c r="F31" t="s">
+        <v>80</v>
+      </c>
+      <c r="G31" t="s">
+        <v>44</v>
+      </c>
+      <c r="H31" t="s">
+        <v>44</v>
+      </c>
+      <c r="L31">
         <v>3</v>
       </c>
-      <c r="S30" t="s">
-        <v>44</v>
-      </c>
-      <c r="V30" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA30" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE30" t="s">
+      <c r="S31" t="s">
+        <v>44</v>
+      </c>
+      <c r="V31" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE31" t="s">
         <v>44</v>
       </c>
     </row>

--- a/data/k-props/2026-08-28.xlsx
+++ b/data/k-props/2026-08-28.xlsx
@@ -166,121 +166,121 @@
     <t>Drew Anderson</t>
   </si>
   <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Eury Pérez</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Washington Nationals</t>
+  </si>
+  <si>
+    <t>Michael Wacha</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Tanner Bibee</t>
+  </si>
+  <si>
+    <t>Hunter Brown</t>
+  </si>
+  <si>
+    <t>Houston Astros @ New York Mets</t>
+  </si>
+  <si>
+    <t>Christian Scott</t>
+  </si>
+  <si>
+    <t>Casey Mize</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Shane McClanahan</t>
+  </si>
+  <si>
+    <t>Emerson Hancock</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>Dylan Cease</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Tomoyuki Sugano</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Grant Holmes</t>
+  </si>
+  <si>
+    <t>Patrick Sandoval</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Cam Schlittler</t>
+  </si>
+  <si>
+    <t>Cody Bradford</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Logan Henderson</t>
+  </si>
+  <si>
+    <t>Luis Castillo</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Dean Kremer</t>
+  </si>
+  <si>
+    <t>Jared Jones</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ St. Louis Cardinals</t>
+  </si>
+  <si>
+    <t>Andrew Painter</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Reid Detmers</t>
+  </si>
+  <si>
+    <t>Brandon Young</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Athletics</t>
+  </si>
+  <si>
+    <t>Jacob Lopez</t>
+  </si>
+  <si>
+    <t>Kohl Drake</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ San Francisco Giants</t>
+  </si>
+  <si>
     <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Eury Pérez</t>
-  </si>
-  <si>
-    <t>Miami Marlins @ Washington Nationals</t>
-  </si>
-  <si>
-    <t>Michael Wacha</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Tanner Bibee</t>
-  </si>
-  <si>
-    <t>Hunter Brown</t>
-  </si>
-  <si>
-    <t>Houston Astros @ New York Mets</t>
-  </si>
-  <si>
-    <t>Christian Scott</t>
-  </si>
-  <si>
-    <t>Casey Mize</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Shane McClanahan</t>
-  </si>
-  <si>
-    <t>Emerson Hancock</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>Dylan Cease</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Tomoyuki Sugano</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Grant Holmes</t>
-  </si>
-  <si>
-    <t>Patrick Sandoval</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Cam Schlittler</t>
-  </si>
-  <si>
-    <t>Cody Bradford</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Logan Henderson</t>
-  </si>
-  <si>
-    <t>Luis Castillo</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Dean Kremer</t>
-  </si>
-  <si>
-    <t>Jared Jones</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ St. Louis Cardinals</t>
-  </si>
-  <si>
-    <t>Andrew Painter</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Reid Detmers</t>
-  </si>
-  <si>
-    <t>Brandon Young</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ Athletics</t>
-  </si>
-  <si>
-    <t>Jacob Lopez</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Kohl Drake</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ San Francisco Giants</t>
   </si>
   <si>
     <t>Blade Tidwell</t>
@@ -866,7 +866,7 @@
         <v>0.216</v>
       </c>
       <c r="X2">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y2">
         <v>0.9439</v>
@@ -878,7 +878,7 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
@@ -887,13 +887,13 @@
         <v>0.1649</v>
       </c>
       <c r="AG2">
-        <v>0.9492</v>
+        <v>0.946</v>
       </c>
       <c r="AH2">
         <v>0.24</v>
       </c>
       <c r="AM2">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -967,7 +967,7 @@
         <v>0.2487</v>
       </c>
       <c r="X3">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y3">
         <v>1.0713</v>
@@ -979,7 +979,7 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>6.29</v>
+        <v>6.27</v>
       </c>
       <c r="AE3" t="s">
         <v>47</v>
@@ -988,13 +988,13 @@
         <v>0.2167</v>
       </c>
       <c r="AG3">
-        <v>1.1853</v>
+        <v>1.1813</v>
       </c>
       <c r="AH3">
         <v>-0.58</v>
       </c>
       <c r="AM3">
-        <v>5.71</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1068,7 +1068,7 @@
         <v>0.2272</v>
       </c>
       <c r="X4">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y4">
         <v>0.9941</v>
@@ -1080,7 +1080,7 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>6.73</v>
+        <v>6.71</v>
       </c>
       <c r="AE4" t="s">
         <v>47</v>
@@ -1089,13 +1089,13 @@
         <v>0.3016</v>
       </c>
       <c r="AG4">
-        <v>0.9491</v>
+        <v>0.9459</v>
       </c>
       <c r="AH4">
         <v>-0.58</v>
       </c>
       <c r="AM4">
-        <v>6.15</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1124,10 +1124,10 @@
         <v>51</v>
       </c>
       <c r="I5">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -1136,22 +1136,22 @@
         <v>4</v>
       </c>
       <c r="M5">
-        <v>0.2615</v>
+        <v>0.2635</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="P5">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="Q5">
-        <v>0.2143</v>
+        <v>0.1948</v>
       </c>
       <c r="R5">
-        <v>0.296</v>
+        <v>0.278</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
@@ -1169,7 +1169,7 @@
         <v>0.2067</v>
       </c>
       <c r="X5">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y5">
         <v>0.971</v>
@@ -1181,22 +1181,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>4.09</v>
+        <v>2.9</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.2475</v>
+        <v>0.2444</v>
       </c>
       <c r="AG5">
-        <v>0.9547</v>
+        <v>0.9515</v>
       </c>
       <c r="AH5">
         <v>0.24</v>
       </c>
       <c r="AM5">
-        <v>4.33</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1270,7 +1270,7 @@
         <v>0.2058</v>
       </c>
       <c r="X6">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y6">
         <v>1.0228</v>
@@ -1282,7 +1282,7 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>6.26</v>
+        <v>6.24</v>
       </c>
       <c r="AE6" t="s">
         <v>47</v>
@@ -1291,13 +1291,13 @@
         <v>0.2665</v>
       </c>
       <c r="AG6">
-        <v>1.0258</v>
+        <v>1.0224</v>
       </c>
       <c r="AH6">
         <v>-0.58</v>
       </c>
       <c r="AM6">
-        <v>5.68</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1371,7 +1371,7 @@
         <v>0.2103</v>
       </c>
       <c r="X7">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y7">
         <v>0.88</v>
@@ -1383,7 +1383,7 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
@@ -1392,13 +1392,13 @@
         <v>0.1884</v>
       </c>
       <c r="AG7">
-        <v>0.8208</v>
+        <v>0.818</v>
       </c>
       <c r="AH7">
         <v>0.24</v>
       </c>
       <c r="AM7">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1472,7 +1472,7 @@
         <v>0.2075</v>
       </c>
       <c r="X8">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y8">
         <v>0.9542</v>
@@ -1484,7 +1484,7 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
@@ -1493,13 +1493,13 @@
         <v>0.1976</v>
       </c>
       <c r="AG8">
-        <v>0.817</v>
+        <v>0.8143</v>
       </c>
       <c r="AH8">
         <v>0.24</v>
       </c>
       <c r="AM8">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1573,7 +1573,7 @@
         <v>0.2232</v>
       </c>
       <c r="X9">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y9">
         <v>0.947</v>
@@ -1585,7 +1585,7 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.86</v>
+        <v>4.84</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
@@ -1594,13 +1594,13 @@
         <v>0.2357</v>
       </c>
       <c r="AG9">
-        <v>0.9671</v>
+        <v>0.9638</v>
       </c>
       <c r="AH9">
         <v>0.24</v>
       </c>
       <c r="AM9">
-        <v>5.1</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1674,7 +1674,7 @@
         <v>0.2191</v>
       </c>
       <c r="X10">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y10">
         <v>0.9963</v>
@@ -1686,7 +1686,7 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>5.93</v>
+        <v>5.91</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
@@ -1695,13 +1695,13 @@
         <v>0.2819</v>
       </c>
       <c r="AG10">
-        <v>1.0291</v>
+        <v>1.0256</v>
       </c>
       <c r="AH10">
         <v>0.24</v>
       </c>
       <c r="AM10">
-        <v>6.17</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1775,7 +1775,7 @@
         <v>0.187</v>
       </c>
       <c r="X11">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y11">
         <v>0.88</v>
@@ -1787,7 +1787,7 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
@@ -1796,13 +1796,13 @@
         <v>0.1931</v>
       </c>
       <c r="AG11">
-        <v>0.7191</v>
+        <v>0.7167</v>
       </c>
       <c r="AH11">
         <v>0.24</v>
       </c>
       <c r="AM11">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1876,7 +1876,7 @@
         <v>0.2232</v>
       </c>
       <c r="X12">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y12">
         <v>1.028</v>
@@ -1888,7 +1888,7 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
@@ -1897,13 +1897,13 @@
         <v>0.2135</v>
       </c>
       <c r="AG12">
-        <v>0.9118</v>
+        <v>0.9087</v>
       </c>
       <c r="AH12">
         <v>0.24</v>
       </c>
       <c r="AM12">
-        <v>4.27</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1977,7 +1977,7 @@
         <v>0.1885</v>
       </c>
       <c r="X13">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y13">
         <v>0.9887</v>
@@ -1989,7 +1989,7 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.56</v>
+        <v>4.54</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
@@ -1998,13 +1998,13 @@
         <v>0.225</v>
       </c>
       <c r="AG13">
-        <v>0.9053</v>
+        <v>0.9022</v>
       </c>
       <c r="AH13">
         <v>0.24</v>
       </c>
       <c r="AM13">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2078,7 +2078,7 @@
         <v>0.2256</v>
       </c>
       <c r="X14">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y14">
         <v>0.9451</v>
@@ -2090,7 +2090,7 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>9.6</v>
+        <v>9.57</v>
       </c>
       <c r="AE14" t="s">
         <v>66</v>
@@ -2099,13 +2099,13 @@
         <v>0.3546</v>
       </c>
       <c r="AG14">
-        <v>1.1873</v>
+        <v>1.1833</v>
       </c>
       <c r="AH14">
         <v>-0.95</v>
       </c>
       <c r="AM14">
-        <v>8.65</v>
+        <v>8.62</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2179,7 +2179,7 @@
         <v>0.2212</v>
       </c>
       <c r="X15">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y15">
         <v>0.9527</v>
@@ -2191,7 +2191,7 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
@@ -2200,13 +2200,13 @@
         <v>0.1367</v>
       </c>
       <c r="AG15">
-        <v>1.0873</v>
+        <v>1.0836</v>
       </c>
       <c r="AH15">
         <v>0.24</v>
       </c>
       <c r="AM15">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2280,7 +2280,7 @@
         <v>0.2184</v>
       </c>
       <c r="X16">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y16">
         <v>1.0808</v>
@@ -2292,7 +2292,7 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>4.92</v>
+        <v>4.9</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
@@ -2301,13 +2301,13 @@
         <v>0.1785</v>
       </c>
       <c r="AG16">
-        <v>1.1944</v>
+        <v>1.1903</v>
       </c>
       <c r="AH16">
         <v>0.24</v>
       </c>
       <c r="AM16">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2381,7 +2381,7 @@
         <v>0.2479</v>
       </c>
       <c r="X17">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y17">
         <v>0.9905</v>
@@ -2393,7 +2393,7 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>5.9</v>
+        <v>5.88</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
@@ -2402,13 +2402,13 @@
         <v>0.2268</v>
       </c>
       <c r="AG17">
-        <v>1.1413</v>
+        <v>1.1374</v>
       </c>
       <c r="AH17">
         <v>0.24</v>
       </c>
       <c r="AM17">
-        <v>6.14</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2482,7 +2482,7 @@
         <v>0.2131</v>
       </c>
       <c r="X18">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y18">
         <v>1.0264</v>
@@ -2494,7 +2494,7 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>6.03</v>
+        <v>6</v>
       </c>
       <c r="AE18" t="s">
         <v>47</v>
@@ -2503,13 +2503,13 @@
         <v>0.3127</v>
       </c>
       <c r="AG18">
-        <v>0.8084</v>
+        <v>0.8056</v>
       </c>
       <c r="AH18">
         <v>-0.58</v>
       </c>
       <c r="AM18">
-        <v>5.45</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2583,7 +2583,7 @@
         <v>0.2175</v>
       </c>
       <c r="X19">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y19">
         <v>1.0232</v>
@@ -2595,7 +2595,7 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
@@ -2604,13 +2604,13 @@
         <v>0.1494</v>
       </c>
       <c r="AG19">
-        <v>0.9879</v>
+        <v>0.9845</v>
       </c>
       <c r="AH19">
         <v>0.24</v>
       </c>
       <c r="AM19">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2684,7 +2684,7 @@
         <v>0.223</v>
       </c>
       <c r="X20">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y20">
         <v>1.0904</v>
@@ -2696,7 +2696,7 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>7.37</v>
+        <v>7.35</v>
       </c>
       <c r="AE20" t="s">
         <v>66</v>
@@ -2705,13 +2705,13 @@
         <v>0.2907</v>
       </c>
       <c r="AG20">
-        <v>1.1454</v>
+        <v>1.1415</v>
       </c>
       <c r="AH20">
         <v>-0.95</v>
       </c>
       <c r="AM20">
-        <v>6.42</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2785,7 +2785,7 @@
         <v>0.2077</v>
       </c>
       <c r="X21">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y21">
         <v>0.9332</v>
@@ -2797,7 +2797,7 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
@@ -2806,13 +2806,13 @@
         <v>0.1981</v>
       </c>
       <c r="AG21">
-        <v>0.8464</v>
+        <v>0.8435</v>
       </c>
       <c r="AH21">
         <v>0.24</v>
       </c>
       <c r="AM21">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2886,7 +2886,7 @@
         <v>0.2369</v>
       </c>
       <c r="X22">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y22">
         <v>1.0791</v>
@@ -2898,7 +2898,7 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>6.19</v>
+        <v>6.17</v>
       </c>
       <c r="AE22" t="s">
         <v>47</v>
@@ -2907,13 +2907,13 @@
         <v>0.2347</v>
       </c>
       <c r="AG22">
-        <v>1.1249</v>
+        <v>1.1211</v>
       </c>
       <c r="AH22">
         <v>-0.58</v>
       </c>
       <c r="AM22">
-        <v>5.61</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2987,7 +2987,7 @@
         <v>0.2155</v>
       </c>
       <c r="X23">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y23">
         <v>0.911</v>
@@ -2999,7 +2999,7 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
@@ -3008,13 +3008,13 @@
         <v>0.2534</v>
       </c>
       <c r="AG23">
-        <v>1.1678</v>
+        <v>1.1639</v>
       </c>
       <c r="AH23">
         <v>0.24</v>
       </c>
       <c r="AM23">
-        <v>5.43</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3088,7 +3088,7 @@
         <v>0.252</v>
       </c>
       <c r="X24">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y24">
         <v>1.0671</v>
@@ -3100,7 +3100,7 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
@@ -3109,13 +3109,13 @@
         <v>0.2075</v>
       </c>
       <c r="AG24">
-        <v>1.0912</v>
+        <v>1.0875</v>
       </c>
       <c r="AH24">
         <v>0.24</v>
       </c>
       <c r="AM24">
-        <v>5.44</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3189,7 +3189,7 @@
         <v>0.2269</v>
       </c>
       <c r="X25">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y25">
         <v>0.9462</v>
@@ -3201,7 +3201,7 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>5.15</v>
+        <v>5.13</v>
       </c>
       <c r="AE25" t="s">
         <v>45</v>
@@ -3210,13 +3210,13 @@
         <v>0.3002</v>
       </c>
       <c r="AG25">
-        <v>0.7821</v>
+        <v>0.7794</v>
       </c>
       <c r="AH25">
         <v>0.24</v>
       </c>
       <c r="AM25">
-        <v>5.39</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3290,7 +3290,7 @@
         <v>0.2148</v>
       </c>
       <c r="X26">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y26">
         <v>1.0058</v>
@@ -3302,7 +3302,7 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
@@ -3311,13 +3311,13 @@
         <v>0.1797</v>
       </c>
       <c r="AG26">
-        <v>0.9577</v>
+        <v>0.9545</v>
       </c>
       <c r="AH26">
         <v>0.24</v>
       </c>
       <c r="AM26">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3376,25 +3376,25 @@
         <v>0.369</v>
       </c>
       <c r="S27" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="T27">
-        <v>0.2627</v>
+        <v>0.2734</v>
       </c>
       <c r="U27">
-        <v>0.2436</v>
+        <v>0.264</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>0.2586</v>
       </c>
       <c r="X27">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y27">
-        <v>1.0521</v>
+        <v>1.116</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3403,22 +3403,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>6.6</v>
+        <v>7.26</v>
       </c>
       <c r="AE27" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="AF27">
         <v>0.247</v>
       </c>
       <c r="AG27">
-        <v>1.2012</v>
+        <v>1.2459</v>
       </c>
       <c r="AH27">
-        <v>-0.58</v>
+        <v>-0.95</v>
       </c>
       <c r="AM27">
-        <v>6.02</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3426,16 +3426,16 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" t="s">
         <v>88</v>
-      </c>
-      <c r="F28" t="s">
-        <v>89</v>
       </c>
       <c r="G28">
         <v>823178</v>
       </c>
       <c r="H28" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="I28">
         <v>4.2</v>
@@ -3483,7 +3483,7 @@
         <v>0.2347</v>
       </c>
       <c r="X28">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y28">
         <v>1.0126</v>
@@ -3495,7 +3495,7 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="AE28" t="s">
         <v>45</v>
@@ -3504,13 +3504,13 @@
         <v>0.1688</v>
       </c>
       <c r="AG28">
-        <v>1.0724</v>
+        <v>1.0688</v>
       </c>
       <c r="AH28">
         <v>0.24</v>
       </c>
       <c r="AM28">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3521,7 +3521,7 @@
         <v>90</v>
       </c>
       <c r="F29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G29">
         <v>823178</v>
@@ -3560,13 +3560,13 @@
         <v>0.296</v>
       </c>
       <c r="S29" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="T29">
-        <v>0.1731</v>
+        <v>0.1847</v>
       </c>
       <c r="U29">
-        <v>0.1743</v>
+        <v>0.1736</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -3575,10 +3575,10 @@
         <v>0.1969</v>
       </c>
       <c r="X29">
-        <v>0.2187</v>
+        <v>0.2194</v>
       </c>
       <c r="Y29">
-        <v>0.9439</v>
+        <v>0.88</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3587,7 +3587,7 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="AE29" t="s">
         <v>45</v>
@@ -3596,13 +3596,13 @@
         <v>0.205</v>
       </c>
       <c r="AG29">
-        <v>0.7915</v>
+        <v>0.8416</v>
       </c>
       <c r="AH29">
         <v>0.24</v>
       </c>
       <c r="AM29">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">

--- a/data/k-props/2026-08-28.xlsx
+++ b/data/k-props/2026-08-28.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="97">
   <si>
     <t>date</t>
   </si>
@@ -145,6 +145,9 @@
     <t>lineup_unweighted_30d_posted</t>
   </si>
   <si>
+    <t>O</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -154,6 +157,9 @@
     <t>David Peterson</t>
   </si>
   <si>
+    <t>W</t>
+  </si>
+  <si>
     <t>6-7</t>
   </si>
   <si>
@@ -169,10 +175,16 @@
     <t>Opener / bullpen game</t>
   </si>
   <si>
+    <t>L</t>
+  </si>
+  <si>
     <t>Eury Pérez</t>
   </si>
   <si>
     <t>Miami Marlins @ Washington Nationals</t>
+  </si>
+  <si>
+    <t>U</t>
   </si>
   <si>
     <t>Michael Wacha</t>
@@ -871,17 +883,23 @@
       <c r="Y2">
         <v>0.9439</v>
       </c>
+      <c r="Z2">
+        <v>5</v>
+      </c>
       <c r="AA2" t="s">
         <v>44</v>
       </c>
+      <c r="AB2">
+        <v>0.02</v>
+      </c>
       <c r="AC2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD2">
         <v>3.28</v>
       </c>
       <c r="AE2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF2">
         <v>0.1649</v>
@@ -891,6 +909,18 @@
       </c>
       <c r="AH2">
         <v>0.24</v>
+      </c>
+      <c r="AI2">
+        <v>1.72</v>
+      </c>
+      <c r="AJ2">
+        <v>1.72</v>
+      </c>
+      <c r="AK2">
+        <v>1.48</v>
+      </c>
+      <c r="AL2">
+        <v>1.48</v>
       </c>
       <c r="AM2">
         <v>3.52</v>
@@ -901,7 +931,7 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>4.5</v>
@@ -972,17 +1002,23 @@
       <c r="Y3">
         <v>1.0713</v>
       </c>
+      <c r="Z3">
+        <v>6</v>
+      </c>
       <c r="AA3" t="s">
         <v>44</v>
       </c>
+      <c r="AB3">
+        <v>1.19</v>
+      </c>
       <c r="AC3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD3">
         <v>6.27</v>
       </c>
       <c r="AE3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF3">
         <v>0.2167</v>
@@ -992,6 +1028,18 @@
       </c>
       <c r="AH3">
         <v>-0.58</v>
+      </c>
+      <c r="AI3">
+        <v>-0.27</v>
+      </c>
+      <c r="AJ3">
+        <v>0.27</v>
+      </c>
+      <c r="AK3">
+        <v>0.31</v>
+      </c>
+      <c r="AL3">
+        <v>0.31</v>
       </c>
       <c r="AM3">
         <v>5.69</v>
@@ -1002,7 +1050,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>6.5</v>
@@ -1014,7 +1062,7 @@
         <v>130</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <v>824231</v>
@@ -1073,17 +1121,23 @@
       <c r="Y4">
         <v>0.9941</v>
       </c>
+      <c r="Z4">
+        <v>7</v>
+      </c>
       <c r="AA4" t="s">
         <v>44</v>
       </c>
+      <c r="AB4">
+        <v>-0.37</v>
+      </c>
       <c r="AC4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD4">
         <v>6.71</v>
       </c>
       <c r="AE4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF4">
         <v>0.3016</v>
@@ -1093,6 +1147,18 @@
       </c>
       <c r="AH4">
         <v>-0.58</v>
+      </c>
+      <c r="AI4">
+        <v>0.29</v>
+      </c>
+      <c r="AJ4">
+        <v>0.29</v>
+      </c>
+      <c r="AK4">
+        <v>0.87</v>
+      </c>
+      <c r="AL4">
+        <v>0.87</v>
       </c>
       <c r="AM4">
         <v>6.13</v>
@@ -1103,7 +1169,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -1115,13 +1181,13 @@
         <v>-120</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G5">
         <v>824231</v>
       </c>
       <c r="H5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I5">
         <v>3</v>
@@ -1174,17 +1240,23 @@
       <c r="Y5">
         <v>0.971</v>
       </c>
+      <c r="Z5">
+        <v>5</v>
+      </c>
       <c r="AA5" t="s">
         <v>44</v>
       </c>
+      <c r="AB5">
+        <v>-1.36</v>
+      </c>
       <c r="AC5" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="AD5">
         <v>2.9</v>
       </c>
       <c r="AE5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF5">
         <v>0.2444</v>
@@ -1194,6 +1266,18 @@
       </c>
       <c r="AH5">
         <v>0.24</v>
+      </c>
+      <c r="AI5">
+        <v>2.1</v>
+      </c>
+      <c r="AJ5">
+        <v>2.1</v>
+      </c>
+      <c r="AK5">
+        <v>1.86</v>
+      </c>
+      <c r="AL5">
+        <v>1.86</v>
       </c>
       <c r="AM5">
         <v>3.14</v>
@@ -1204,7 +1288,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C6">
         <v>5.5</v>
@@ -1216,7 +1300,7 @@
         <v>-111</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>822691</v>
@@ -1275,17 +1359,23 @@
       <c r="Y6">
         <v>1.0228</v>
       </c>
+      <c r="Z6">
+        <v>5</v>
+      </c>
       <c r="AA6" t="s">
-        <v>44</v>
+        <v>57</v>
+      </c>
+      <c r="AB6">
+        <v>0.16</v>
       </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD6">
         <v>6.24</v>
       </c>
       <c r="AE6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF6">
         <v>0.2665</v>
@@ -1295,6 +1385,18 @@
       </c>
       <c r="AH6">
         <v>-0.58</v>
+      </c>
+      <c r="AI6">
+        <v>-1.24</v>
+      </c>
+      <c r="AJ6">
+        <v>1.24</v>
+      </c>
+      <c r="AK6">
+        <v>-0.66</v>
+      </c>
+      <c r="AL6">
+        <v>0.66</v>
       </c>
       <c r="AM6">
         <v>5.66</v>
@@ -1305,7 +1407,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C7">
         <v>4.5</v>
@@ -1317,7 +1419,7 @@
         <v>-160</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>824396</v>
@@ -1376,17 +1478,23 @@
       <c r="Y7">
         <v>0.88</v>
       </c>
+      <c r="Z7">
+        <v>10</v>
+      </c>
       <c r="AA7" t="s">
         <v>44</v>
       </c>
+      <c r="AB7">
+        <v>-0.83</v>
+      </c>
       <c r="AC7" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="AD7">
         <v>3.43</v>
       </c>
       <c r="AE7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF7">
         <v>0.1884</v>
@@ -1396,6 +1504,18 @@
       </c>
       <c r="AH7">
         <v>0.24</v>
+      </c>
+      <c r="AI7">
+        <v>6.57</v>
+      </c>
+      <c r="AJ7">
+        <v>6.57</v>
+      </c>
+      <c r="AK7">
+        <v>6.33</v>
+      </c>
+      <c r="AL7">
+        <v>6.33</v>
       </c>
       <c r="AM7">
         <v>3.67</v>
@@ -1406,7 +1526,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C8">
         <v>4.5</v>
@@ -1418,7 +1538,7 @@
         <v>106</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>824396</v>
@@ -1477,17 +1597,23 @@
       <c r="Y8">
         <v>0.9542</v>
       </c>
+      <c r="Z8">
+        <v>5</v>
+      </c>
       <c r="AA8" t="s">
         <v>44</v>
       </c>
+      <c r="AB8">
+        <v>-0.64</v>
+      </c>
       <c r="AC8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD8">
         <v>3.62</v>
       </c>
       <c r="AE8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF8">
         <v>0.1976</v>
@@ -1497,6 +1623,18 @@
       </c>
       <c r="AH8">
         <v>0.24</v>
+      </c>
+      <c r="AI8">
+        <v>1.38</v>
+      </c>
+      <c r="AJ8">
+        <v>1.38</v>
+      </c>
+      <c r="AK8">
+        <v>1.14</v>
+      </c>
+      <c r="AL8">
+        <v>1.14</v>
       </c>
       <c r="AM8">
         <v>3.86</v>
@@ -1507,7 +1645,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C9">
         <v>5.5</v>
@@ -1519,7 +1657,7 @@
         <v>-135</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G9">
         <v>823583</v>
@@ -1578,17 +1716,23 @@
       <c r="Y9">
         <v>0.947</v>
       </c>
+      <c r="Z9">
+        <v>10</v>
+      </c>
       <c r="AA9" t="s">
         <v>44</v>
       </c>
+      <c r="AB9">
+        <v>-0.42</v>
+      </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD9">
         <v>4.84</v>
       </c>
       <c r="AE9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF9">
         <v>0.2357</v>
@@ -1598,6 +1742,18 @@
       </c>
       <c r="AH9">
         <v>0.24</v>
+      </c>
+      <c r="AI9">
+        <v>5.16</v>
+      </c>
+      <c r="AJ9">
+        <v>5.16</v>
+      </c>
+      <c r="AK9">
+        <v>4.92</v>
+      </c>
+      <c r="AL9">
+        <v>4.92</v>
       </c>
       <c r="AM9">
         <v>5.08</v>
@@ -1608,7 +1764,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C10">
         <v>5.5</v>
@@ -1620,7 +1776,7 @@
         <v>140</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>823583</v>
@@ -1679,17 +1835,23 @@
       <c r="Y10">
         <v>0.9963</v>
       </c>
+      <c r="Z10">
+        <v>2</v>
+      </c>
       <c r="AA10" t="s">
-        <v>44</v>
+        <v>57</v>
+      </c>
+      <c r="AB10">
+        <v>0.65</v>
       </c>
       <c r="AC10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD10">
         <v>5.91</v>
       </c>
       <c r="AE10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF10">
         <v>0.2819</v>
@@ -1699,6 +1861,18 @@
       </c>
       <c r="AH10">
         <v>0.24</v>
+      </c>
+      <c r="AI10">
+        <v>-3.91</v>
+      </c>
+      <c r="AJ10">
+        <v>3.91</v>
+      </c>
+      <c r="AK10">
+        <v>-4.15</v>
+      </c>
+      <c r="AL10">
+        <v>4.15</v>
       </c>
       <c r="AM10">
         <v>6.15</v>
@@ -1709,7 +1883,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C11">
         <v>3.5</v>
@@ -1721,7 +1895,7 @@
         <v>110</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G11">
         <v>822935</v>
@@ -1780,17 +1954,23 @@
       <c r="Y11">
         <v>0.88</v>
       </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
       <c r="AA11" t="s">
-        <v>44</v>
+        <v>57</v>
+      </c>
+      <c r="AB11">
+        <v>-0.7</v>
       </c>
       <c r="AC11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD11">
         <v>2.56</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF11">
         <v>0.1931</v>
@@ -1800,6 +1980,18 @@
       </c>
       <c r="AH11">
         <v>0.24</v>
+      </c>
+      <c r="AI11">
+        <v>-1.56</v>
+      </c>
+      <c r="AJ11">
+        <v>1.56</v>
+      </c>
+      <c r="AK11">
+        <v>-1.8</v>
+      </c>
+      <c r="AL11">
+        <v>1.8</v>
       </c>
       <c r="AM11">
         <v>2.8</v>
@@ -1810,7 +2002,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1822,7 +2014,7 @@
         <v>-122</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>822935</v>
@@ -1881,17 +2073,23 @@
       <c r="Y12">
         <v>1.028</v>
       </c>
+      <c r="Z12">
+        <v>4</v>
+      </c>
       <c r="AA12" t="s">
-        <v>44</v>
+        <v>57</v>
+      </c>
+      <c r="AB12">
+        <v>-0.24</v>
       </c>
       <c r="AC12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD12">
         <v>4.02</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF12">
         <v>0.2135</v>
@@ -1901,6 +2099,18 @@
       </c>
       <c r="AH12">
         <v>0.24</v>
+      </c>
+      <c r="AI12">
+        <v>-0.02</v>
+      </c>
+      <c r="AJ12">
+        <v>0.02</v>
+      </c>
+      <c r="AK12">
+        <v>-0.26</v>
+      </c>
+      <c r="AL12">
+        <v>0.26</v>
       </c>
       <c r="AM12">
         <v>4.26</v>
@@ -1911,7 +2121,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C13">
         <v>3.5</v>
@@ -1923,7 +2133,7 @@
         <v>-104</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G13">
         <v>822769</v>
@@ -1982,17 +2192,23 @@
       <c r="Y13">
         <v>0.9887</v>
       </c>
+      <c r="Z13">
+        <v>1</v>
+      </c>
       <c r="AA13" t="s">
-        <v>44</v>
+        <v>57</v>
+      </c>
+      <c r="AB13">
+        <v>1.28</v>
       </c>
       <c r="AC13" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="AD13">
         <v>4.54</v>
       </c>
       <c r="AE13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF13">
         <v>0.225</v>
@@ -2002,6 +2218,18 @@
       </c>
       <c r="AH13">
         <v>0.24</v>
+      </c>
+      <c r="AI13">
+        <v>-3.54</v>
+      </c>
+      <c r="AJ13">
+        <v>3.54</v>
+      </c>
+      <c r="AK13">
+        <v>-3.78</v>
+      </c>
+      <c r="AL13">
+        <v>3.78</v>
       </c>
       <c r="AM13">
         <v>4.78</v>
@@ -2012,7 +2240,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C14">
         <v>7.5</v>
@@ -2024,7 +2252,7 @@
         <v>102</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G14">
         <v>822769</v>
@@ -2083,17 +2311,23 @@
       <c r="Y14">
         <v>0.9451</v>
       </c>
+      <c r="Z14">
+        <v>8</v>
+      </c>
       <c r="AA14" t="s">
         <v>44</v>
       </c>
+      <c r="AB14">
+        <v>1.12</v>
+      </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD14">
         <v>9.57</v>
       </c>
       <c r="AE14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="AF14">
         <v>0.3546</v>
@@ -2103,6 +2337,18 @@
       </c>
       <c r="AH14">
         <v>-0.95</v>
+      </c>
+      <c r="AI14">
+        <v>-1.57</v>
+      </c>
+      <c r="AJ14">
+        <v>1.57</v>
+      </c>
+      <c r="AK14">
+        <v>-0.62</v>
+      </c>
+      <c r="AL14">
+        <v>0.62</v>
       </c>
       <c r="AM14">
         <v>8.62</v>
@@ -2113,7 +2359,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C15">
         <v>2.5</v>
@@ -2125,7 +2371,7 @@
         <v>145</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G15">
         <v>824877</v>
@@ -2184,17 +2430,23 @@
       <c r="Y15">
         <v>0.9527</v>
       </c>
+      <c r="Z15">
+        <v>4</v>
+      </c>
       <c r="AA15" t="s">
         <v>44</v>
       </c>
+      <c r="AB15">
+        <v>0.91</v>
+      </c>
       <c r="AC15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD15">
         <v>3.17</v>
       </c>
       <c r="AE15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF15">
         <v>0.1367</v>
@@ -2204,6 +2456,18 @@
       </c>
       <c r="AH15">
         <v>0.24</v>
+      </c>
+      <c r="AI15">
+        <v>0.83</v>
+      </c>
+      <c r="AJ15">
+        <v>0.83</v>
+      </c>
+      <c r="AK15">
+        <v>0.59</v>
+      </c>
+      <c r="AL15">
+        <v>0.59</v>
       </c>
       <c r="AM15">
         <v>3.41</v>
@@ -2214,7 +2478,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C16">
         <v>4.5</v>
@@ -2226,7 +2490,7 @@
         <v>-115</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G16">
         <v>824877</v>
@@ -2285,17 +2549,23 @@
       <c r="Y16">
         <v>1.0808</v>
       </c>
+      <c r="Z16">
+        <v>3</v>
+      </c>
       <c r="AA16" t="s">
-        <v>44</v>
+        <v>57</v>
+      </c>
+      <c r="AB16">
+        <v>0.64</v>
       </c>
       <c r="AC16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD16">
         <v>4.9</v>
       </c>
       <c r="AE16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF16">
         <v>0.1785</v>
@@ -2305,6 +2575,18 @@
       </c>
       <c r="AH16">
         <v>0.24</v>
+      </c>
+      <c r="AI16">
+        <v>-1.9</v>
+      </c>
+      <c r="AJ16">
+        <v>1.9</v>
+      </c>
+      <c r="AK16">
+        <v>-2.14</v>
+      </c>
+      <c r="AL16">
+        <v>2.14</v>
       </c>
       <c r="AM16">
         <v>5.14</v>
@@ -2315,7 +2597,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C17">
         <v>5.5</v>
@@ -2327,7 +2609,7 @@
         <v>-104</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G17">
         <v>823504</v>
@@ -2386,17 +2668,23 @@
       <c r="Y17">
         <v>0.9905</v>
       </c>
+      <c r="Z17">
+        <v>7</v>
+      </c>
       <c r="AA17" t="s">
         <v>44</v>
       </c>
+      <c r="AB17">
+        <v>0.62</v>
+      </c>
       <c r="AC17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD17">
         <v>5.88</v>
       </c>
       <c r="AE17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF17">
         <v>0.2268</v>
@@ -2406,6 +2694,18 @@
       </c>
       <c r="AH17">
         <v>0.24</v>
+      </c>
+      <c r="AI17">
+        <v>1.12</v>
+      </c>
+      <c r="AJ17">
+        <v>1.12</v>
+      </c>
+      <c r="AK17">
+        <v>0.88</v>
+      </c>
+      <c r="AL17">
+        <v>0.88</v>
       </c>
       <c r="AM17">
         <v>6.12</v>
@@ -2416,7 +2716,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C18">
         <v>6.5</v>
@@ -2428,7 +2728,7 @@
         <v>104</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G18">
         <v>823504</v>
@@ -2487,17 +2787,23 @@
       <c r="Y18">
         <v>1.0264</v>
       </c>
+      <c r="Z18">
+        <v>8</v>
+      </c>
       <c r="AA18" t="s">
         <v>44</v>
       </c>
+      <c r="AB18">
+        <v>-1.08</v>
+      </c>
       <c r="AC18" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="AD18">
         <v>6</v>
       </c>
       <c r="AE18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF18">
         <v>0.3127</v>
@@ -2507,6 +2813,18 @@
       </c>
       <c r="AH18">
         <v>-0.58</v>
+      </c>
+      <c r="AI18">
+        <v>2</v>
+      </c>
+      <c r="AJ18">
+        <v>2</v>
+      </c>
+      <c r="AK18">
+        <v>2.58</v>
+      </c>
+      <c r="AL18">
+        <v>2.58</v>
       </c>
       <c r="AM18">
         <v>5.42</v>
@@ -2517,7 +2835,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C19">
         <v>3.5</v>
@@ -2529,7 +2847,7 @@
         <v>115</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G19">
         <v>823744</v>
@@ -2588,17 +2906,23 @@
       <c r="Y19">
         <v>1.0232</v>
       </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
       <c r="AA19" t="s">
-        <v>44</v>
+        <v>57</v>
+      </c>
+      <c r="AB19">
+        <v>0.01</v>
       </c>
       <c r="AC19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD19">
         <v>3.27</v>
       </c>
       <c r="AE19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF19">
         <v>0.1494</v>
@@ -2608,6 +2932,18 @@
       </c>
       <c r="AH19">
         <v>0.24</v>
+      </c>
+      <c r="AI19">
+        <v>-3.27</v>
+      </c>
+      <c r="AJ19">
+        <v>3.27</v>
+      </c>
+      <c r="AK19">
+        <v>-3.51</v>
+      </c>
+      <c r="AL19">
+        <v>3.51</v>
       </c>
       <c r="AM19">
         <v>3.51</v>
@@ -2618,7 +2954,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C20">
         <v>6.5</v>
@@ -2630,7 +2966,7 @@
         <v>-111</v>
       </c>
       <c r="F20" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G20">
         <v>823744</v>
@@ -2689,17 +3025,23 @@
       <c r="Y20">
         <v>1.0904</v>
       </c>
+      <c r="Z20">
+        <v>7</v>
+      </c>
       <c r="AA20" t="s">
         <v>44</v>
       </c>
+      <c r="AB20">
+        <v>-0.1</v>
+      </c>
       <c r="AC20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD20">
         <v>7.35</v>
       </c>
       <c r="AE20" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="AF20">
         <v>0.2907</v>
@@ -2709,6 +3051,18 @@
       </c>
       <c r="AH20">
         <v>-0.95</v>
+      </c>
+      <c r="AI20">
+        <v>-0.35</v>
+      </c>
+      <c r="AJ20">
+        <v>0.35</v>
+      </c>
+      <c r="AK20">
+        <v>0.6</v>
+      </c>
+      <c r="AL20">
+        <v>0.6</v>
       </c>
       <c r="AM20">
         <v>6.4</v>
@@ -2719,7 +3073,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C21">
         <v>3.5</v>
@@ -2731,7 +3085,7 @@
         <v>134</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G21">
         <v>823666</v>
@@ -2790,17 +3144,23 @@
       <c r="Y21">
         <v>0.9332</v>
       </c>
+      <c r="Z21">
+        <v>1</v>
+      </c>
       <c r="AA21" t="s">
-        <v>44</v>
+        <v>57</v>
+      </c>
+      <c r="AB21">
+        <v>0.26</v>
       </c>
       <c r="AC21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD21">
         <v>3.52</v>
       </c>
       <c r="AE21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF21">
         <v>0.1981</v>
@@ -2810,6 +3170,18 @@
       </c>
       <c r="AH21">
         <v>0.24</v>
+      </c>
+      <c r="AI21">
+        <v>-2.52</v>
+      </c>
+      <c r="AJ21">
+        <v>2.52</v>
+      </c>
+      <c r="AK21">
+        <v>-2.76</v>
+      </c>
+      <c r="AL21">
+        <v>2.76</v>
       </c>
       <c r="AM21">
         <v>3.76</v>
@@ -2820,7 +3192,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C22">
         <v>5.5</v>
@@ -2832,7 +3204,7 @@
         <v>-138</v>
       </c>
       <c r="F22" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G22">
         <v>823666</v>
@@ -2891,17 +3263,23 @@
       <c r="Y22">
         <v>1.0791</v>
       </c>
+      <c r="Z22">
+        <v>3</v>
+      </c>
       <c r="AA22" t="s">
-        <v>44</v>
+        <v>57</v>
+      </c>
+      <c r="AB22">
+        <v>0.09</v>
       </c>
       <c r="AC22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD22">
         <v>6.17</v>
       </c>
       <c r="AE22" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF22">
         <v>0.2347</v>
@@ -2911,6 +3289,18 @@
       </c>
       <c r="AH22">
         <v>-0.58</v>
+      </c>
+      <c r="AI22">
+        <v>-3.17</v>
+      </c>
+      <c r="AJ22">
+        <v>3.17</v>
+      </c>
+      <c r="AK22">
+        <v>-2.59</v>
+      </c>
+      <c r="AL22">
+        <v>2.59</v>
       </c>
       <c r="AM22">
         <v>5.59</v>
@@ -2921,7 +3311,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C23">
         <v>4.5</v>
@@ -2933,7 +3323,7 @@
         <v>115</v>
       </c>
       <c r="F23" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G23">
         <v>823013</v>
@@ -2992,17 +3382,23 @@
       <c r="Y23">
         <v>0.911</v>
       </c>
+      <c r="Z23">
+        <v>6</v>
+      </c>
       <c r="AA23" t="s">
         <v>44</v>
       </c>
+      <c r="AB23">
+        <v>0.92</v>
+      </c>
       <c r="AC23" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD23">
         <v>5.18</v>
       </c>
       <c r="AE23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF23">
         <v>0.2534</v>
@@ -3012,6 +3408,18 @@
       </c>
       <c r="AH23">
         <v>0.24</v>
+      </c>
+      <c r="AI23">
+        <v>0.82</v>
+      </c>
+      <c r="AJ23">
+        <v>0.82</v>
+      </c>
+      <c r="AK23">
+        <v>0.58</v>
+      </c>
+      <c r="AL23">
+        <v>0.58</v>
       </c>
       <c r="AM23">
         <v>5.42</v>
@@ -3022,7 +3430,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C24">
         <v>5.5</v>
@@ -3034,7 +3442,7 @@
         <v>-156</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G24">
         <v>823985</v>
@@ -3093,17 +3501,23 @@
       <c r="Y24">
         <v>1.0671</v>
       </c>
+      <c r="Z24">
+        <v>6</v>
+      </c>
       <c r="AA24" t="s">
         <v>44</v>
       </c>
+      <c r="AB24">
+        <v>-0.08</v>
+      </c>
       <c r="AC24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD24">
         <v>5.18</v>
       </c>
       <c r="AE24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF24">
         <v>0.2075</v>
@@ -3113,6 +3527,18 @@
       </c>
       <c r="AH24">
         <v>0.24</v>
+      </c>
+      <c r="AI24">
+        <v>0.82</v>
+      </c>
+      <c r="AJ24">
+        <v>0.82</v>
+      </c>
+      <c r="AK24">
+        <v>0.58</v>
+      </c>
+      <c r="AL24">
+        <v>0.58</v>
       </c>
       <c r="AM24">
         <v>5.42</v>
@@ -3123,7 +3549,7 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C25">
         <v>6.5</v>
@@ -3135,7 +3561,7 @@
         <v>-102</v>
       </c>
       <c r="F25" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G25">
         <v>823985</v>
@@ -3194,17 +3620,23 @@
       <c r="Y25">
         <v>0.9462</v>
       </c>
+      <c r="Z25">
+        <v>2</v>
+      </c>
       <c r="AA25" t="s">
-        <v>44</v>
+        <v>57</v>
+      </c>
+      <c r="AB25">
+        <v>-1.13</v>
       </c>
       <c r="AC25" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD25">
         <v>5.13</v>
       </c>
       <c r="AE25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF25">
         <v>0.3002</v>
@@ -3214,6 +3646,18 @@
       </c>
       <c r="AH25">
         <v>0.24</v>
+      </c>
+      <c r="AI25">
+        <v>-3.13</v>
+      </c>
+      <c r="AJ25">
+        <v>3.13</v>
+      </c>
+      <c r="AK25">
+        <v>-3.37</v>
+      </c>
+      <c r="AL25">
+        <v>3.37</v>
       </c>
       <c r="AM25">
         <v>5.37</v>
@@ -3224,7 +3668,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C26">
         <v>4.5</v>
@@ -3236,7 +3680,7 @@
         <v>-142</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G26">
         <v>824960</v>
@@ -3295,17 +3739,23 @@
       <c r="Y26">
         <v>1.0058</v>
       </c>
+      <c r="Z26">
+        <v>4</v>
+      </c>
       <c r="AA26" t="s">
-        <v>44</v>
+        <v>57</v>
+      </c>
+      <c r="AB26">
+        <v>-0.11</v>
       </c>
       <c r="AC26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD26">
         <v>4.15</v>
       </c>
       <c r="AE26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF26">
         <v>0.1797</v>
@@ -3315,6 +3765,18 @@
       </c>
       <c r="AH26">
         <v>0.24</v>
+      </c>
+      <c r="AI26">
+        <v>-0.15</v>
+      </c>
+      <c r="AJ26">
+        <v>0.15</v>
+      </c>
+      <c r="AK26">
+        <v>-0.39</v>
+      </c>
+      <c r="AL26">
+        <v>0.39</v>
       </c>
       <c r="AM26">
         <v>4.39</v>
@@ -3325,7 +3787,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C27">
         <v>6.5</v>
@@ -3337,7 +3799,7 @@
         <v>-142</v>
       </c>
       <c r="F27" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G27">
         <v>824960</v>
@@ -3396,17 +3858,23 @@
       <c r="Y27">
         <v>1.116</v>
       </c>
+      <c r="Z27">
+        <v>6</v>
+      </c>
       <c r="AA27" t="s">
-        <v>44</v>
+        <v>57</v>
+      </c>
+      <c r="AB27">
+        <v>-0.19</v>
       </c>
       <c r="AC27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD27">
         <v>7.26</v>
       </c>
       <c r="AE27" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="AF27">
         <v>0.247</v>
@@ -3416,6 +3884,18 @@
       </c>
       <c r="AH27">
         <v>-0.95</v>
+      </c>
+      <c r="AI27">
+        <v>-1.26</v>
+      </c>
+      <c r="AJ27">
+        <v>1.26</v>
+      </c>
+      <c r="AK27">
+        <v>-0.31</v>
+      </c>
+      <c r="AL27">
+        <v>0.31</v>
       </c>
       <c r="AM27">
         <v>6.31</v>
@@ -3426,16 +3906,16 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G28">
         <v>823178</v>
       </c>
       <c r="H28" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I28">
         <v>4.2</v>
@@ -3489,16 +3969,16 @@
         <v>1.0126</v>
       </c>
       <c r="AA28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD28">
         <v>3.52</v>
       </c>
       <c r="AE28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF28">
         <v>0.1688</v>
@@ -3518,10 +3998,10 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F29" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G29">
         <v>823178</v>
@@ -3581,16 +4061,16 @@
         <v>0.88</v>
       </c>
       <c r="AA29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD29">
         <v>3.15</v>
       </c>
       <c r="AE29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF29">
         <v>0.205</v>
@@ -3610,7 +4090,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C30">
         <v>3.5</v>
@@ -3622,31 +4102,31 @@
         <v>132</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L30">
         <v>4</v>
       </c>
       <c r="S30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3654,7 +4134,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C31">
         <v>4.5</v>
@@ -3666,31 +4146,34 @@
         <v>126</v>
       </c>
       <c r="F31" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L31">
         <v>3</v>
       </c>
       <c r="S31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V31" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="Z31">
+        <v>7</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
       </c>
       <c r="AC31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
